--- a/tame_output/ON/bt/strategyON_20240510.xlsx
+++ b/tame_output/ON/bt/strategyON_20240510.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>59.7%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.6%</t>
+          <t>-79.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>114.0%</t>
+          <t>114.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>134.0%</t>
+          <t>135.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>92.4%</t>
+          <t>92.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-55.8%</t>
+          <t>-53.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.5%</t>
+          <t>-75.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>94.5%</t>
+          <t>95.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>444.3%</t>
+          <t>444.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.1%</t>
+          <t>-8.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-607.3%</t>
+          <t>-605.9%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,22 +1140,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-8.1%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.6%</t>
+          <t>-40.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-2.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-42.2%</t>
+          <t>-36.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-285.1%</t>
+          <t>-284.5%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-32.9%</t>
+          <t>-32.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.6%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>71.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>68.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-34.4%</t>
+          <t>-34.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-26.3%</t>
+          <t>-25.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>41.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-154.0%</t>
+          <t>-149.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-284.9%</t>
+          <t>-277.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.4%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-29.4%</t>
+          <t>-29.6%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-213.1%</t>
+          <t>-208.7%</t>
         </is>
       </c>
     </row>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923089</v>
+        <v>3.41997943392309</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776679</v>
+        <v>3.50044609677668</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.402085240579135</v>
+        <v>-9.275880984781383</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.6126241027637191</v>
+        <v>-0.5621424004446181</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.700083598490133</v>
+        <v>-2.573879342692381</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.528516258687603</v>
+        <v>1.604238812166254</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.32201544504133</v>
+        <v>-9.195811189243578</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.5812293633278403</v>
+        <v>-0.5307476610087392</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.620013802952329</v>
+        <v>-2.493809547154577</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.575924957231042</v>
+        <v>1.651647510709694</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.78732685376181</v>
+        <v>3.787326853761809</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.088534222811731</v>
+        <v>-8.962329967013979</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.4799124455981483</v>
+        <v>-0.4294307432790472</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.386532580722731</v>
+        <v>-2.260328324924978</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.723938119406654</v>
+        <v>1.799660672885305</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255787</v>
+        <v>3.801633547255786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.908825692667858</v>
+        <v>-8.782621436870105</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.4109212438535579</v>
+        <v>-0.3604395415344568</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.329361076560035</v>
+        <v>-2.203156820762282</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.755348811591312</v>
+        <v>1.831071365069963</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860429</v>
+        <v>3.763178672860427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.77655021903697</v>
+        <v>-8.650345963239218</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.3626435676541759</v>
+        <v>-0.3121618653350748</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.197085602929148</v>
+        <v>-2.070881347131396</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.830081582516871</v>
+        <v>1.905804135995522</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575955</v>
+        <v>3.784715218575953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.585950544363817</v>
+        <v>-8.459746288566064</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.283588637097278</v>
+        <v>-0.2331069347781769</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.006485928255995</v>
+        <v>-1.880281672458243</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.947256448008399</v>
+        <v>2.022979001487051</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430989</v>
+        <v>3.753878996430987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.336950745680236</v>
+        <v>-8.210746489882483</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.1710823764001868</v>
+        <v>-0.1206006740810857</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.006485928255995</v>
+        <v>-1.880281672458243</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.960162789232058</v>
+        <v>2.035885342710709</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077645</v>
+        <v>3.692928280077643</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.44254073545334</v>
+        <v>-8.316336479655588</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.341294301908647</v>
+        <v>-0.2908125995895463</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.1120759180291</v>
+        <v>-1.985871662231347</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.768832865768977</v>
+        <v>1.844555419247628</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457903</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.461275637571937</v>
+        <v>-8.335071381774185</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.3002439208789998</v>
+        <v>-0.2497622185598987</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.1120759180291</v>
+        <v>-1.985871662231347</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.817377207646063</v>
+        <v>1.893099761124714</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180811</v>
+        <v>3.760330111180809</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.313335596164338</v>
+        <v>-8.187131340366586</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.3609468270041276</v>
+        <v>-0.3104651246850265</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.091755002120542</v>
+        <v>-1.96555074632279</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.70969083450303</v>
+        <v>1.785413387981681</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879204</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.289106959775365</v>
+        <v>-8.162902703977613</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.3599693587020165</v>
+        <v>-0.3094876563829159</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.06752636573157</v>
+        <v>-1.941322109933818</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.715514030082935</v>
+        <v>1.791236583561587</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568109</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.245558553004674</v>
+        <v>-8.119354297206922</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.3495106080888331</v>
+        <v>-0.2990289057697324</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.06752636573157</v>
+        <v>-1.941322109933818</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.708553417987842</v>
+        <v>1.784275971466494</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.78291895796342</v>
+        <v>3.782918957963418</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.003410159550816</v>
+        <v>-7.877205903753064</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.2381888963261467</v>
+        <v>-0.1877071940070461</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.06752636573157</v>
+        <v>-1.941322109933818</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.723015772368985</v>
+        <v>1.798738325847637</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192818</v>
+        <v>3.828547911192817</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.940180787782467</v>
+        <v>-7.813976531984715</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.2183650271596127</v>
+        <v>-0.1678833248405116</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.06752636573157</v>
+        <v>-1.941322109933818</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.71754789282818</v>
+        <v>1.793270446306832</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262049</v>
+        <v>3.828049353262047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.816889652965337</v>
+        <v>-7.690685397167584</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.1715504792221831</v>
+        <v>-0.1210687769030825</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.94423523091444</v>
+        <v>-1.818030975116687</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.789020667729035</v>
+        <v>1.864743221207687</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389911</v>
+        <v>3.812450103389909</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.795740454061893</v>
+        <v>-7.669536198264141</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.1553898214234808</v>
+        <v>-0.1049081191043797</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.923086032010997</v>
+        <v>-1.796881776213244</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.809411165308426</v>
+        <v>1.885133718787078</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788096</v>
+        <v>3.748324832788094</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.551975012078449</v>
+        <v>-7.425770756280697</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.0621029362830523</v>
+        <v>-0.01162123396395165</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.923086032010997</v>
+        <v>-1.796881776213244</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.805191873655477</v>
+        <v>1.880914427134128</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527527</v>
+        <v>3.824307657527525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.287946944885189</v>
+        <v>-7.161742689087436</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.04563260451426787</v>
+        <v>0.09611430683336852</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.721220633195043</v>
+        <v>-1.59501637739729</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.928435426865065</v>
+        <v>2.004157980343717</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749186</v>
+        <v>3.826351398749184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.038096550936114</v>
+        <v>-6.911892295138362</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.1383148370776</v>
+        <v>0.1887965393967006</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.721220633195043</v>
+        <v>-1.59501637739729</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.921177501848767</v>
+        <v>1.996900055327419</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481499</v>
+        <v>3.835954411481497</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.862204458468682</v>
+        <v>-6.73600020267093</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.2122707975852212</v>
+        <v>0.2627524999043223</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.721220633195043</v>
+        <v>-1.59501637739729</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.924776625369416</v>
+        <v>2.000499178848067</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862989</v>
+        <v>3.780930335862987</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.690757995446218</v>
+        <v>-6.564553739648466</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.2941768888487606</v>
+        <v>0.3446585911678612</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.54977417017258</v>
+        <v>-1.423569914374827</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.040972009237448</v>
+        <v>2.116694562716099</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102783</v>
+        <v>3.773761647102782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.465724995777395</v>
+        <v>-6.339520739979643</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.3832105663325867</v>
+        <v>0.4336922686516873</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.324741170503757</v>
+        <v>-1.198536914706004</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.175012286655038</v>
+        <v>2.25073484013369</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353076</v>
+        <v>3.764614304353074</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.251090618140989</v>
+        <v>-6.124886362343236</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.4737591184414667</v>
+        <v>0.5242408207605673</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.11010679286735</v>
+        <v>-0.9839025370695973</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.3084877142912</v>
+        <v>2.384210267769851</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544785</v>
+        <v>3.798811195544783</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.15809057693509</v>
+        <v>-6.031886321137338</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4921533937076217</v>
+        <v>0.5426350960267223</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.11010679286735</v>
+        <v>-0.9839025370695973</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.289681973074996</v>
+        <v>2.365404526553647</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712296</v>
+        <v>3.797691308712294</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.91766008013023</v>
+        <v>-5.791455824332478</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.590068669054443</v>
+        <v>0.6405503713735441</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.8696762960624898</v>
+        <v>-0.743472040264737</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.435683347782789</v>
+        <v>2.51140590126144</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837688</v>
+        <v>3.821589933837686</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.845417511959035</v>
+        <v>-5.719213256161283</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6228950101577411</v>
+        <v>0.6733767124768422</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.8696762960624898</v>
+        <v>-0.743472040264737</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.439612661617609</v>
+        <v>2.515335215096261</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349969</v>
+        <v>3.822323422349967</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.72947766233385</v>
+        <v>-5.603273406536098</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6699495339251551</v>
+        <v>0.7204312362442562</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.7928545650463659</v>
+        <v>-0.6666503092486131</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.486384284144624</v>
+        <v>2.562106837623275</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972343</v>
+        <v>3.848613050972341</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.486822073910687</v>
+        <v>-5.360617818112935</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7640098405144138</v>
+        <v>0.8144915428335149</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.7928545650463659</v>
+        <v>-0.6666503092486131</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.483382355364617</v>
+        <v>2.559104908843269</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145942</v>
+        <v>3.81866537614594</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.266801275873677</v>
+        <v>-5.140597020075925</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8535971967398321</v>
+        <v>0.9040788990589332</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.6516347199783856</v>
+        <v>-0.5254304641806329</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.569693299416019</v>
+        <v>2.645415852894671</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009954</v>
+        <v>3.843270952009952</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.067552645968868</v>
+        <v>-4.941348390171115</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9491908315035791</v>
+        <v>0.9996725338226802</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.6516347199783856</v>
+        <v>-0.5254304641806329</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.585587482217842</v>
+        <v>2.661310035696494</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966262</v>
+        <v>3.845043810966259</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.908037542449498</v>
+        <v>-4.781833286651746</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.014142717351629</v>
+        <v>1.06462441967073</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.4921196164590157</v>
+        <v>-0.365915360661263</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.682442388769766</v>
+        <v>2.758164942248418</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046999</v>
+        <v>3.791269976046996</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.76336539734976</v>
+        <v>-4.637161141552008</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.082099677952964</v>
+        <v>1.132581380272065</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.3474474713592783</v>
+        <v>-0.2212432155615255</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.779333778391049</v>
+        <v>2.8550563318697</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412106</v>
+        <v>3.735835647412103</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.823240224707453</v>
+        <v>-4.697035968909701</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.044187238411313</v>
+        <v>1.094668940730414</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.4073222987169704</v>
+        <v>-0.2811180429192177</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.729446373377859</v>
+        <v>2.805168926856511</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144519</v>
+        <v>3.762643902144516</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.736440726928445</v>
+        <v>-4.610236471130692</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.101307530845482</v>
+        <v>1.151789233164583</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.4073222987169704</v>
+        <v>-0.2811180429192177</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.751846866700425</v>
+        <v>2.827569420179077</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900696</v>
+        <v>3.729142822900693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.738910433390251</v>
+        <v>-4.612706177592498</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.100392049634172</v>
+        <v>1.150873751953273</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.4097920051787766</v>
+        <v>-0.2835877493810238</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.750437444196754</v>
+        <v>2.826159997675405</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473603</v>
+        <v>3.7432166204736</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.807280619714261</v>
+        <v>-4.681076363916508</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.08405089757927</v>
+        <v>1.134532599898371</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.4005163061425616</v>
+        <v>-0.2743120503448089</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.767009786093185</v>
+        <v>2.842732339571836</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978372</v>
+        <v>3.714175563978369</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.685864190087784</v>
+        <v>-4.559659934290032</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.123054178061752</v>
+        <v>1.173535880380853</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.4005163061425616</v>
+        <v>-0.2743120503448089</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.757446494725076</v>
+        <v>2.833169048203728</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887706</v>
+        <v>3.710903155887703</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.71685734941649</v>
+        <v>-4.590653093618737</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9353664793706564</v>
+        <v>0.9858481816897573</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.4005163061425616</v>
+        <v>-0.2743120503448089</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.582156059765463</v>
+        <v>2.657878613244114</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675905</v>
+        <v>3.746038950675901</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.54138308962402</v>
+        <v>-4.415178833826268</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.010123415279432</v>
+        <v>1.060605117598533</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.4005163061425616</v>
+        <v>-0.2743120503448089</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.58672329175725</v>
+        <v>2.662445845235902</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695449</v>
+        <v>3.765020747695446</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.652319342265269</v>
+        <v>-4.526115086467517</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9414909429841396</v>
+        <v>0.9919726453032405</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.4005163061425616</v>
+        <v>-0.2743120503448089</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.562465320518458</v>
+        <v>2.638187873997109</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581294</v>
+        <v>3.773206721581291</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.855345919808502</v>
+        <v>-4.72914166401075</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8634116971867518</v>
+        <v>0.9138933995058527</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.603542883685795</v>
+        <v>-0.4773386278880423</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.443780759212423</v>
+        <v>2.519503312691075</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734163</v>
+        <v>3.78434037673416</v>
       </c>
       <c r="C1942" t="n">
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.697420320873209</v>
+        <v>-4.571216065075457</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9367543231930013</v>
+        <v>0.9872360255121022</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.603542883685795</v>
+        <v>-0.4773386278880423</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.453953145644555</v>
+        <v>2.529675699123207</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869463822123</v>
+        <v>3.786946382212296</v>
       </c>
       <c r="C1943" t="n">
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.845741574684338</v>
+        <v>-4.719537318886585</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8723720922424101</v>
+        <v>0.9228537945615112</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.603542883685795</v>
+        <v>-0.4773386278880423</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.448899416218416</v>
+        <v>2.524621969697067</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786047</v>
+        <v>3.752023923786044</v>
       </c>
       <c r="C1944" t="n">
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.846924659335398</v>
+        <v>-4.720720403537646</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8636746338265116</v>
+        <v>0.9141563361456124</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.6091859321523065</v>
+        <v>-0.4829816763545538</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.437289362583035</v>
+        <v>2.513011916061686</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273192</v>
+        <v>3.753567590273189</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.723796952341315</v>
+        <v>-4.597592696543563</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9134775896572462</v>
+        <v>0.9639592919763471</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.6091859321523065</v>
+        <v>-0.4829816763545538</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.437841235616136</v>
+        <v>2.513563789094788</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279502</v>
+        <v>3.733387025279498</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.630986470890456</v>
+        <v>-4.504782215092703</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8798744741289557</v>
+        <v>0.9303561764480568</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.5163754507014472</v>
+        <v>-0.3901711949036945</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.422800216378017</v>
+        <v>2.498522769856669</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030429</v>
+        <v>3.748282241030426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.582423418669426</v>
+        <v>-4.456219162871673</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9011731709419686</v>
+        <v>0.9516548732610695</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.467812398480417</v>
+        <v>-0.3416081426826643</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.453811523635236</v>
+        <v>2.529534077113888</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942741</v>
+        <v>3.721073619942738</v>
       </c>
       <c r="C1948" t="n">
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.469752200433176</v>
+        <v>-4.343547944635423</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9413173667481916</v>
+        <v>0.9917990690672926</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.3551411802441668</v>
+        <v>-0.2289369244464141</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.516489963088709</v>
+        <v>2.592212516567361</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268539</v>
+        <v>3.743044028268535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.357375199250503</v>
+        <v>-4.23117094345275</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.991759463051928</v>
+        <v>1.042241165371029</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.3551411802441668</v>
+        <v>-0.2289369244464141</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.521981258919376</v>
+        <v>2.597703812398028</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968865</v>
+        <v>3.689594264968861</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.555609768137233</v>
+        <v>-4.429405512339481</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9239628372657749</v>
+        <v>0.9744445395848758</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.5533757491308974</v>
+        <v>-0.4271714933331446</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.414537719355877</v>
+        <v>2.490260272834529</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175325</v>
+        <v>3.643066046175321</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.638611049162512</v>
+        <v>-4.51240679336476</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7291180448563166</v>
+        <v>0.7795997471754175</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.5719466336580712</v>
+        <v>-0.4457423778603184</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.241750908640226</v>
+        <v>2.317473462118878</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199272</v>
+        <v>3.682712735199268</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.479416777105936</v>
+        <v>-4.353212521308183</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9129454143981528</v>
+        <v>0.9634271167172537</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.5719466336580712</v>
+        <v>-0.4457423778603184</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.361900569359432</v>
+        <v>2.437623122838084</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660771</v>
+        <v>3.733008865660768</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.566015360087039</v>
+        <v>-4.439811104289286</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8928190073080347</v>
+        <v>0.9433007096271355</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.5719466336580712</v>
+        <v>-0.4457423778603184</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.376413595461755</v>
+        <v>2.452136148940407</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383427</v>
+        <v>3.741170494383423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.527631697528887</v>
+        <v>-4.401427441731135</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9055919136736637</v>
+        <v>0.9560736159927647</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.53356297109992</v>
+        <v>-0.4073587153021672</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.396863234339014</v>
+        <v>2.472585787817666</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002488</v>
+        <v>3.751143622002484</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.350515367493721</v>
+        <v>-4.224311111695969</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9731674745330321</v>
+        <v>1.023649176852133</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.53356297109992</v>
+        <v>-0.4073587153021672</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.393592263184316</v>
+        <v>2.469314816662968</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263905</v>
+        <v>3.741324873263902</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.320813243517428</v>
+        <v>-4.194608987719675</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9857317158854626</v>
+        <v>1.036213418204563</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.5380330963152333</v>
+        <v>-0.4118288405174806</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.391593579817041</v>
+        <v>2.467316133295693</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.75072580148124</v>
+        <v>3.750725801481236</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.14143782227866</v>
+        <v>-4.015233566480908</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.051268859687384</v>
+        <v>1.101750562006485</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.3812563381445147</v>
+        <v>-0.2550520823467619</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.479446610025887</v>
+        <v>2.555169163504539</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452235</v>
+        <v>3.716988143452231</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.186452035799267</v>
+        <v>-4.060247780001514</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.014070629610731</v>
+        <v>1.064552331929832</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.4116052334591193</v>
+        <v>-0.2854009776613665</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.442044728168714</v>
+        <v>2.517767281647366</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.885561952960605</v>
+        <v>3.878134958323731</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.457627611069811</v>
+        <v>-4.443399443689896</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9112919618414592</v>
+        <v>0.9169832287934252</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.6088397155730354</v>
+        <v>-0.5365130064492487</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.32939560123931</v>
+        <v>2.372791626713582</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240510.xlsx
+++ b/tame_output/ON/bt/strategyON_20240510.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.0%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.1%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>24.6%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>44.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -921,12 +921,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>114.8%</t>
+          <t>113.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>135.0%</t>
+          <t>133.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>92.9%</t>
+          <t>91.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-53.8%</t>
+          <t>-55.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.6%</t>
+          <t>-77.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>95.2%</t>
+          <t>94.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>444.5%</t>
+          <t>441.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.9%</t>
+          <t>-9.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-605.9%</t>
+          <t>-615.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,57 +1140,57 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-8.1%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.9%</t>
+          <t>-40.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-2.1%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-36.2%</t>
+          <t>-40.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-0.1%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-284.5%</t>
+          <t>-288.4%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-32.3%</t>
+          <t>-33.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>69.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>71.0%</t>
+          <t>70.5%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-34.7%</t>
+          <t>-34.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-25.5%</t>
+          <t>-29.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.4%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>41.0%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-149.0%</t>
+          <t>-157.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-277.6%</t>
+          <t>-294.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-29.6%</t>
+          <t>-29.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-15.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-208.7%</t>
+          <t>-218.7%</t>
         </is>
       </c>
     </row>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50044609677668</v>
+        <v>3.500446096776679</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.275880984781383</v>
+        <v>-9.402085240579135</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.5621424004446181</v>
+        <v>-0.6126241027637191</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.573879342692381</v>
+        <v>-2.700083598490133</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.604238812166254</v>
+        <v>1.528516258687603</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.195811189243578</v>
+        <v>-9.32201544504133</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.5307476610087392</v>
+        <v>-0.5812293633278403</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.493809547154577</v>
+        <v>-2.620013802952329</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.651647510709694</v>
+        <v>1.575924957231042</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761809</v>
+        <v>3.78732685376181</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.962329967013979</v>
+        <v>-9.088534222811731</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.4294307432790472</v>
+        <v>-0.4799124455981483</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.260328324924978</v>
+        <v>-2.386532580722731</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.799660672885305</v>
+        <v>1.723938119406654</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255786</v>
+        <v>3.801633547255787</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.782621436870105</v>
+        <v>-8.908825692667858</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.3604395415344568</v>
+        <v>-0.4109212438535579</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.203156820762282</v>
+        <v>-2.329361076560035</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.831071365069963</v>
+        <v>1.755348811591312</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860427</v>
+        <v>3.763178672860429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.650345963239218</v>
+        <v>-8.77655021903697</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.3121618653350748</v>
+        <v>-0.3626435676541759</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.070881347131396</v>
+        <v>-2.197085602929148</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.905804135995522</v>
+        <v>1.830081582516871</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575953</v>
+        <v>3.784715218575955</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.459746288566064</v>
+        <v>-8.585950544363817</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.2331069347781769</v>
+        <v>-0.283588637097278</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.880281672458243</v>
+        <v>-2.006485928255995</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.022979001487051</v>
+        <v>1.947256448008399</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430987</v>
+        <v>3.753878996430989</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.210746489882483</v>
+        <v>-8.336950745680236</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.1206006740810857</v>
+        <v>-0.1710823764001868</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.880281672458243</v>
+        <v>-2.006485928255995</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.035885342710709</v>
+        <v>1.960162789232058</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077643</v>
+        <v>3.692928280077645</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.316336479655588</v>
+        <v>-8.44254073545334</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.2908125995895463</v>
+        <v>-0.341294301908647</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.985871662231347</v>
+        <v>-2.1120759180291</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.844555419247628</v>
+        <v>1.768832865768977</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.770419008457903</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.335071381774185</v>
+        <v>-8.461275637571937</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.2497622185598987</v>
+        <v>-0.3002439208789998</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.985871662231347</v>
+        <v>-2.1120759180291</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.893099761124714</v>
+        <v>1.817377207646063</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180809</v>
+        <v>3.760330111180811</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.187131340366586</v>
+        <v>-8.313335596164338</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.3104651246850265</v>
+        <v>-0.3609468270041276</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.96555074632279</v>
+        <v>-2.091755002120542</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.785413387981681</v>
+        <v>1.70969083450303</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.723562653879204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.162902703977613</v>
+        <v>-8.289106959775365</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.3094876563829159</v>
+        <v>-0.3599693587020165</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.941322109933818</v>
+        <v>-2.06752636573157</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.791236583561587</v>
+        <v>1.715514030082935</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568109</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.119354297206922</v>
+        <v>-8.245558553004674</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.2990289057697324</v>
+        <v>-0.3495106080888331</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.941322109933818</v>
+        <v>-2.06752636573157</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.784275971466494</v>
+        <v>1.708553417987842</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963418</v>
+        <v>3.78291895796342</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.877205903753064</v>
+        <v>-8.003410159550816</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.1877071940070461</v>
+        <v>-0.2381888963261467</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.941322109933818</v>
+        <v>-2.06752636573157</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.798738325847637</v>
+        <v>1.723015772368985</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192817</v>
+        <v>3.828547911192818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.813976531984715</v>
+        <v>-7.940180787782467</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.1678833248405116</v>
+        <v>-0.2183650271596127</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.941322109933818</v>
+        <v>-2.06752636573157</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.793270446306832</v>
+        <v>1.71754789282818</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262047</v>
+        <v>3.828049353262049</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.690685397167584</v>
+        <v>-7.816889652965337</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.1210687769030825</v>
+        <v>-0.1715504792221831</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.818030975116687</v>
+        <v>-1.94423523091444</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.864743221207687</v>
+        <v>1.789020667729035</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389909</v>
+        <v>3.812450103389911</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.669536198264141</v>
+        <v>-7.795740454061893</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.1049081191043797</v>
+        <v>-0.1553898214234808</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.796881776213244</v>
+        <v>-1.923086032010997</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.885133718787078</v>
+        <v>1.809411165308426</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788094</v>
+        <v>3.748324832788096</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.425770756280697</v>
+        <v>-7.551975012078449</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.01162123396395165</v>
+        <v>-0.0621029362830523</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.796881776213244</v>
+        <v>-1.923086032010997</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.880914427134128</v>
+        <v>1.805191873655477</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527525</v>
+        <v>3.824307657527527</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.161742689087436</v>
+        <v>-7.287946944885189</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.09611430683336852</v>
+        <v>0.04563260451426787</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.59501637739729</v>
+        <v>-1.721220633195043</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.004157980343717</v>
+        <v>1.928435426865065</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749184</v>
+        <v>3.826351398749186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.911892295138362</v>
+        <v>-7.038096550936114</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.1887965393967006</v>
+        <v>0.1383148370776</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.59501637739729</v>
+        <v>-1.721220633195043</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.996900055327419</v>
+        <v>1.921177501848767</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481497</v>
+        <v>3.835954411481499</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.73600020267093</v>
+        <v>-6.862204458468682</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.2627524999043223</v>
+        <v>0.2122707975852212</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.59501637739729</v>
+        <v>-1.721220633195043</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.000499178848067</v>
+        <v>1.924776625369416</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862987</v>
+        <v>3.780930335862989</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.564553739648466</v>
+        <v>-6.690757995446218</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.3446585911678612</v>
+        <v>0.2941768888487606</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.423569914374827</v>
+        <v>-1.54977417017258</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.116694562716099</v>
+        <v>2.040972009237448</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102782</v>
+        <v>3.773761647102783</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.339520739979643</v>
+        <v>-6.465724995777395</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.4336922686516873</v>
+        <v>0.3832105663325867</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.198536914706004</v>
+        <v>-1.324741170503757</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.25073484013369</v>
+        <v>2.175012286655038</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353074</v>
+        <v>3.764614304353076</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.124886362343236</v>
+        <v>-6.251090618140989</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5242408207605673</v>
+        <v>0.4737591184414667</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.9839025370695973</v>
+        <v>-1.11010679286735</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.384210267769851</v>
+        <v>2.3084877142912</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544783</v>
+        <v>3.798811195544785</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.031886321137338</v>
+        <v>-6.15809057693509</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5426350960267223</v>
+        <v>0.4921533937076217</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.9839025370695973</v>
+        <v>-1.11010679286735</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.365404526553647</v>
+        <v>2.289681973074996</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712294</v>
+        <v>3.797691308712296</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.791455824332478</v>
+        <v>-5.91766008013023</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6405503713735441</v>
+        <v>0.590068669054443</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.743472040264737</v>
+        <v>-0.8696762960624898</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.51140590126144</v>
+        <v>2.435683347782789</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837686</v>
+        <v>3.821589933837688</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.719213256161283</v>
+        <v>-5.845417511959035</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6733767124768422</v>
+        <v>0.6228950101577411</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.743472040264737</v>
+        <v>-0.8696762960624898</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.515335215096261</v>
+        <v>2.439612661617609</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349967</v>
+        <v>3.822323422349969</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.603273406536098</v>
+        <v>-5.72947766233385</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7204312362442562</v>
+        <v>0.6699495339251551</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.6666503092486131</v>
+        <v>-0.7928545650463659</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.562106837623275</v>
+        <v>2.486384284144624</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972341</v>
+        <v>3.848613050972343</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.360617818112935</v>
+        <v>-5.486822073910687</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8144915428335149</v>
+        <v>0.7640098405144138</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.6666503092486131</v>
+        <v>-0.7928545650463659</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.559104908843269</v>
+        <v>2.483382355364617</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.81866537614594</v>
+        <v>3.818665376145942</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.140597020075925</v>
+        <v>-5.35380488610079</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9040788990589332</v>
+        <v>0.8187957526489869</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.5254304641806329</v>
+        <v>-0.7474420181111837</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.645415852894671</v>
+        <v>2.51220892053634</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009952</v>
+        <v>3.843270952009954</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.941348390171115</v>
+        <v>-5.154556256195981</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9996725338226802</v>
+        <v>0.9143893874127338</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.5254304641806329</v>
+        <v>-0.7474420181111837</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.661310035696494</v>
+        <v>2.528103103338164</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966259</v>
+        <v>3.845043810966262</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.781833286651746</v>
+        <v>-4.995041152676611</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.06462441967073</v>
+        <v>0.9793412732607836</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.365915360661263</v>
+        <v>-0.5879269145918138</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.758164942248418</v>
+        <v>2.624958009890087</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046996</v>
+        <v>3.791269976046999</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.637161141552008</v>
+        <v>-4.850369007576874</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.132581380272065</v>
+        <v>1.047298233862118</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.2212432155615255</v>
+        <v>-0.4432547694920764</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.8550563318697</v>
+        <v>2.72184939951137</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412103</v>
+        <v>3.735835647412106</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.697035968909701</v>
+        <v>-4.910243834934566</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.094668940730414</v>
+        <v>1.009385794320467</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.2811180429192177</v>
+        <v>-0.5031295968497684</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.805168926856511</v>
+        <v>2.67196199449818</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144516</v>
+        <v>3.762643902144519</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.610236471130692</v>
+        <v>-4.823444337155557</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.151789233164583</v>
+        <v>1.066506086754637</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.2811180429192177</v>
+        <v>-0.5031295968497684</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.827569420179077</v>
+        <v>2.694362487820746</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900693</v>
+        <v>3.729142822900696</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.612706177592498</v>
+        <v>-4.825914043617363</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.150873751953273</v>
+        <v>1.065590605543327</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.2835877493810238</v>
+        <v>-0.5055993033115747</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.826159997675405</v>
+        <v>2.692953065317075</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432166204736</v>
+        <v>3.743216620473603</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.681076363916508</v>
+        <v>-4.894284229941373</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.134532599898371</v>
+        <v>1.049249453488425</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.2743120503448089</v>
+        <v>-0.4963236042753597</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.842732339571836</v>
+        <v>2.709525407213506</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978369</v>
+        <v>3.714175563978372</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.559659934290032</v>
+        <v>-4.772867800314897</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.173535880380853</v>
+        <v>1.088252733970907</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.2743120503448089</v>
+        <v>-0.4963236042753597</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.833169048203728</v>
+        <v>2.699962115845397</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887703</v>
+        <v>3.710903155887706</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.590653093618737</v>
+        <v>-4.803860959643602</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9858481816897573</v>
+        <v>0.9005650352798114</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.2743120503448089</v>
+        <v>-0.4963236042753597</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.657878613244114</v>
+        <v>2.524671680885784</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675901</v>
+        <v>3.746038950675905</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.415178833826268</v>
+        <v>-4.628386699851132</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.060605117598533</v>
+        <v>0.975321971188587</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.2743120503448089</v>
+        <v>-0.4963236042753597</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.662445845235902</v>
+        <v>2.529238912877572</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695446</v>
+        <v>3.765020747695449</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.526115086467517</v>
+        <v>-4.739322952492381</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9919726453032405</v>
+        <v>0.9066894988932945</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.2743120503448089</v>
+        <v>-0.4963236042753597</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.638187873997109</v>
+        <v>2.504980941638779</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581291</v>
+        <v>3.773206721581294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.72914166401075</v>
+        <v>-4.942349530035615</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9138933995058527</v>
+        <v>0.8286102530959067</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.4773386278880423</v>
+        <v>-0.6993501818185931</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.519503312691075</v>
+        <v>2.386296380332744</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.78434037673416</v>
+        <v>3.784340376734163</v>
       </c>
       <c r="C1942" t="n">
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.571216065075457</v>
+        <v>-4.784423931100322</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9872360255121022</v>
+        <v>0.9019528791021563</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.4773386278880423</v>
+        <v>-0.6993501818185931</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.529675699123207</v>
+        <v>2.396468766764877</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212296</v>
+        <v>3.7869463822123</v>
       </c>
       <c r="C1943" t="n">
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.719537318886585</v>
+        <v>-4.93274518491145</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9228537945615112</v>
+        <v>0.8375706481515652</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.4773386278880423</v>
+        <v>-0.6993501818185931</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.524621969697067</v>
+        <v>2.391415037338737</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786044</v>
+        <v>3.752023923786047</v>
       </c>
       <c r="C1944" t="n">
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.720720403537646</v>
+        <v>-4.933928269562511</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9141563361456124</v>
+        <v>0.8288731897356665</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.4829816763545538</v>
+        <v>-0.7049932302851046</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.513011916061686</v>
+        <v>2.379804983703356</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273189</v>
+        <v>3.753567590273192</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.597592696543563</v>
+        <v>-4.810800562568428</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9639592919763471</v>
+        <v>0.8786761455664012</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.4829816763545538</v>
+        <v>-0.7049932302851046</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.513563789094788</v>
+        <v>2.380356856736457</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279498</v>
+        <v>3.733387025279502</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.504782215092703</v>
+        <v>-4.717990081117568</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9303561764480568</v>
+        <v>0.8450730300381109</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.3901711949036945</v>
+        <v>-0.6121827488342453</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.498522769856669</v>
+        <v>2.365315837498339</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030426</v>
+        <v>3.748282241030429</v>
       </c>
       <c r="C1947" t="n">
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.456219162871673</v>
+        <v>-4.669427028896538</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9516548732610695</v>
+        <v>0.8663717268511235</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.3416081426826643</v>
+        <v>-0.5636196966132151</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.529534077113888</v>
+        <v>2.396327144755557</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942738</v>
+        <v>3.721073619942741</v>
       </c>
       <c r="C1948" t="n">
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.343547944635423</v>
+        <v>-4.556755810660288</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9917990690672926</v>
+        <v>0.9065159226573467</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.2289369244464141</v>
+        <v>-0.4509484783769649</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.592212516567361</v>
+        <v>2.45900558420903</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268535</v>
+        <v>3.743044028268539</v>
       </c>
       <c r="C1949" t="n">
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.23117094345275</v>
+        <v>-4.444378809477615</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.042241165371029</v>
+        <v>0.9569580189610831</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.2289369244464141</v>
+        <v>-0.4509484783769649</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.597703812398028</v>
+        <v>2.464496880039698</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968861</v>
+        <v>3.689594264968865</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.429405512339481</v>
+        <v>-4.642613378364346</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9744445395848758</v>
+        <v>0.8891613931749298</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.4271714933331446</v>
+        <v>-0.6491830472636955</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.490260272834529</v>
+        <v>2.357053340476198</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175321</v>
+        <v>3.643066046175325</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.51240679336476</v>
+        <v>-4.725614659389625</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7795997471754175</v>
+        <v>0.6943166007654715</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.4457423778603184</v>
+        <v>-0.6677539317908692</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.317473462118878</v>
+        <v>2.184266529760547</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199268</v>
+        <v>3.682712735199272</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.353212521308183</v>
+        <v>-4.566420387333048</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9634271167172537</v>
+        <v>0.8781439703073077</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.4457423778603184</v>
+        <v>-0.6677539317908692</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.437623122838084</v>
+        <v>2.304416190479753</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660768</v>
+        <v>3.733008865660771</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.439811104289286</v>
+        <v>-4.653018970314151</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9433007096271355</v>
+        <v>0.8580175632171896</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.4457423778603184</v>
+        <v>-0.6677539317908692</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.452136148940407</v>
+        <v>2.318929216582076</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383423</v>
+        <v>3.741170494383427</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.401427441731135</v>
+        <v>-4.614635307756</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9560736159927647</v>
+        <v>0.8707904695828188</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.4073587153021672</v>
+        <v>-0.629370269232718</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.472585787817666</v>
+        <v>2.339378855459335</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002484</v>
+        <v>3.751143622002488</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.224311111695969</v>
+        <v>-4.437518977720834</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.023649176852133</v>
+        <v>0.938366030442187</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.4073587153021672</v>
+        <v>-0.629370269232718</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.469314816662968</v>
+        <v>2.336107884304637</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263902</v>
+        <v>3.741324873263905</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.194608987719675</v>
+        <v>-4.40781685374454</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.036213418204563</v>
+        <v>0.9509302717946175</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.4118288405174806</v>
+        <v>-0.6338403944480313</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.467316133295693</v>
+        <v>2.334109200937363</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481236</v>
+        <v>3.75072580148124</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.015233566480908</v>
+        <v>-4.228441432505773</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.101750562006485</v>
+        <v>1.016467415596539</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.2550520823467619</v>
+        <v>-0.4770636362773126</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.555169163504539</v>
+        <v>2.421962231146208</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452231</v>
+        <v>3.716988143452235</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.060247780001514</v>
+        <v>-4.273455646026379</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.064552331929832</v>
+        <v>0.9792691855198861</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.2854009776613665</v>
+        <v>-0.5074125315919172</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.517767281647366</v>
+        <v>2.384560349289035</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.878134958323731</v>
+        <v>3.526277317971208</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.443399443689896</v>
+        <v>-4.540460156298814</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9169832287934252</v>
+        <v>0.8781589437498578</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.5365130064492487</v>
+        <v>-0.7017755696348658</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.372791626713582</v>
+        <v>2.273634088802212</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240510.xlsx
+++ b/tame_output/ON/bt/strategyON_20240510.xlsx
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776679</v>
+        <v>3.50044609677668</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611698</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199888</v>
+        <v>3.496848329199889</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910631</v>
+        <v>3.499968163910632</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078597</v>
+        <v>3.490055666078598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587501888027</v>
+        <v>3.485875018880271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234396</v>
+        <v>3.480688917234397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860585</v>
+        <v>3.493712438860586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792542</v>
+        <v>3.573670449792543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003468962892</v>
+        <v>3.600034689628921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410717</v>
+        <v>3.691568158410718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68515780608528</v>
+        <v>3.685157806085281</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282101</v>
+        <v>3.684840248282102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116216</v>
+        <v>3.710931958116217</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081568</v>
+        <v>3.768948099081569</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425327</v>
+        <v>3.728574354425328</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702411</v>
+        <v>3.747699084702412</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906227</v>
+        <v>3.766313503906228</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>

--- a/tame_output/ON/bt/strategyON_20240510.xlsx
+++ b/tame_output/ON/bt/strategyON_20240510.xlsx
@@ -600,12 +600,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>54.1%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1956</v>
+        <v>1957</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.0%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>25.0%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1956</v>
+        <v>1957</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,7 +824,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-6.2%</t>
+          <t>-10.3%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-6.2%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>44.5%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-42.2%</t>
+          <t>-48.9%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.8%</t>
+          <t>-79.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>113.7%</t>
+          <t>114.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1956</v>
+        <v>1957</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.8%</t>
+          <t>92.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-77.0%</t>
+          <t>-75.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>94.6%</t>
+          <t>94.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>441.0%</t>
+          <t>441.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-615.6%</t>
+          <t>-599.5%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1956</v>
+        <v>1957</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-40.7%</t>
+          <t>-35.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-288.4%</t>
+          <t>-282.0%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-33.9%</t>
+          <t>-32.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.4%</t>
+          <t>69.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1956</v>
+        <v>1957</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-29.6%</t>
+          <t>-27.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>37.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-157.1%</t>
+          <t>-154.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-294.2%</t>
+          <t>-279.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1956</v>
+        <v>1957</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1456,42 +1456,42 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-29.4%</t>
+          <t>-31.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.7%</t>
+          <t>-17.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-218.7%</t>
+          <t>-183.9%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1959"/>
+  <dimension ref="A1:G1960"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297752</v>
+        <v>3.458100091297753</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317619</v>
+        <v>3.44775050131762</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737173</v>
+        <v>3.503515506737174</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50044609677668</v>
+        <v>3.500446096776679</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611698</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199889</v>
+        <v>3.496848329199888</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910632</v>
+        <v>3.499968163910631</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880271</v>
+        <v>3.48587501888027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234397</v>
+        <v>3.480688917234396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860586</v>
+        <v>3.493712438860585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792543</v>
+        <v>3.573670449792542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628921</v>
+        <v>3.60003468962892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410718</v>
+        <v>3.691568158410717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085281</v>
+        <v>3.68515780608528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282102</v>
+        <v>3.684840248282101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116217</v>
+        <v>3.710931958116216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081569</v>
+        <v>3.768948099081568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425328</v>
+        <v>3.728574354425327</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702412</v>
+        <v>3.747699084702411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906228</v>
+        <v>3.766313503906227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.402085240579135</v>
+        <v>-9.275880984781383</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.6126241027637191</v>
+        <v>-0.5621424004446181</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.700083598490133</v>
+        <v>-2.573879342692381</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.528516258687603</v>
+        <v>1.604238812166254</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.32201544504133</v>
+        <v>-9.195811189243578</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.5812293633278403</v>
+        <v>-0.5307476610087392</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.620013802952329</v>
+        <v>-2.493809547154577</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.575924957231042</v>
+        <v>1.651647510709694</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.78732685376181</v>
+        <v>3.787326853761809</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.088534222811731</v>
+        <v>-8.962329967013979</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.4799124455981483</v>
+        <v>-0.4294307432790472</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.386532580722731</v>
+        <v>-2.260328324924978</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.723938119406654</v>
+        <v>1.799660672885305</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255787</v>
+        <v>3.801633547255786</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.908825692667858</v>
+        <v>-8.782621436870105</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.4109212438535579</v>
+        <v>-0.3604395415344568</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.329361076560035</v>
+        <v>-2.203156820762282</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.755348811591312</v>
+        <v>1.831071365069963</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860429</v>
+        <v>3.763178672860427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.77655021903697</v>
+        <v>-8.650345963239218</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.3626435676541759</v>
+        <v>-0.3121618653350748</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.197085602929148</v>
+        <v>-2.070881347131396</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.830081582516871</v>
+        <v>1.905804135995522</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575955</v>
+        <v>3.784715218575953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.585950544363817</v>
+        <v>-8.459746288566064</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.283588637097278</v>
+        <v>-0.2331069347781769</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.006485928255995</v>
+        <v>-1.880281672458243</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.947256448008399</v>
+        <v>2.022979001487051</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430989</v>
+        <v>3.753878996430987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.336950745680236</v>
+        <v>-8.210746489882483</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.1710823764001868</v>
+        <v>-0.1206006740810857</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.006485928255995</v>
+        <v>-1.880281672458243</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.960162789232058</v>
+        <v>2.035885342710709</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077645</v>
+        <v>3.692928280077643</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.44254073545334</v>
+        <v>-8.316336479655588</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.341294301908647</v>
+        <v>-0.2908125995895463</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.1120759180291</v>
+        <v>-1.985871662231347</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.768832865768977</v>
+        <v>1.844555419247628</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457903</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.461275637571937</v>
+        <v>-8.335071381774185</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.3002439208789998</v>
+        <v>-0.2497622185598987</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.1120759180291</v>
+        <v>-1.985871662231347</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.817377207646063</v>
+        <v>1.893099761124714</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180811</v>
+        <v>3.760330111180809</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.313335596164338</v>
+        <v>-8.187131340366586</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.3609468270041276</v>
+        <v>-0.3104651246850265</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.091755002120542</v>
+        <v>-1.96555074632279</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.70969083450303</v>
+        <v>1.785413387981681</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879204</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.289106959775365</v>
+        <v>-8.162902703977613</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.3599693587020165</v>
+        <v>-0.3094876563829159</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.06752636573157</v>
+        <v>-1.941322109933818</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.715514030082935</v>
+        <v>1.791236583561587</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568109</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.245558553004674</v>
+        <v>-8.119354297206922</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.3495106080888331</v>
+        <v>-0.2990289057697324</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.06752636573157</v>
+        <v>-1.941322109933818</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.708553417987842</v>
+        <v>1.784275971466494</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.78291895796342</v>
+        <v>3.782918957963418</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.003410159550816</v>
+        <v>-7.877205903753064</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.2381888963261467</v>
+        <v>-0.1877071940070461</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.06752636573157</v>
+        <v>-1.941322109933818</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.723015772368985</v>
+        <v>1.798738325847637</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192818</v>
+        <v>3.828547911192817</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.940180787782467</v>
+        <v>-7.813976531984715</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.2183650271596127</v>
+        <v>-0.1678833248405116</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.06752636573157</v>
+        <v>-1.941322109933818</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.71754789282818</v>
+        <v>1.793270446306832</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262049</v>
+        <v>3.828049353262047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.816889652965337</v>
+        <v>-7.690685397167584</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.1715504792221831</v>
+        <v>-0.1210687769030825</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.94423523091444</v>
+        <v>-1.818030975116687</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.789020667729035</v>
+        <v>1.864743221207687</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389911</v>
+        <v>3.812450103389909</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.795740454061893</v>
+        <v>-7.669536198264141</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.1553898214234808</v>
+        <v>-0.1049081191043797</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.923086032010997</v>
+        <v>-1.796881776213244</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.809411165308426</v>
+        <v>1.885133718787078</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788096</v>
+        <v>3.748324832788094</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.551975012078449</v>
+        <v>-7.425770756280697</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.0621029362830523</v>
+        <v>-0.01162123396395165</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.923086032010997</v>
+        <v>-1.796881776213244</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.805191873655477</v>
+        <v>1.880914427134128</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527527</v>
+        <v>3.824307657527525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.287946944885189</v>
+        <v>-7.161742689087436</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.04563260451426787</v>
+        <v>0.09611430683336852</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.721220633195043</v>
+        <v>-1.59501637739729</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.928435426865065</v>
+        <v>2.004157980343717</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749186</v>
+        <v>3.826351398749184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.038096550936114</v>
+        <v>-6.911892295138362</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.1383148370776</v>
+        <v>0.1887965393967006</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.721220633195043</v>
+        <v>-1.59501637739729</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.921177501848767</v>
+        <v>1.996900055327419</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481499</v>
+        <v>3.835954411481497</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.862204458468682</v>
+        <v>-6.73600020267093</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.2122707975852212</v>
+        <v>0.2627524999043223</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.721220633195043</v>
+        <v>-1.59501637739729</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.924776625369416</v>
+        <v>2.000499178848067</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862989</v>
+        <v>3.780930335862987</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.690757995446218</v>
+        <v>-6.564553739648466</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.2941768888487606</v>
+        <v>0.3446585911678612</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.54977417017258</v>
+        <v>-1.423569914374827</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.040972009237448</v>
+        <v>2.116694562716099</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102783</v>
+        <v>3.773761647102782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.465724995777395</v>
+        <v>-6.339520739979643</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.3832105663325867</v>
+        <v>0.4336922686516873</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.324741170503757</v>
+        <v>-1.198536914706004</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.175012286655038</v>
+        <v>2.25073484013369</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353076</v>
+        <v>3.764614304353074</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.251090618140989</v>
+        <v>-6.124886362343236</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.4737591184414667</v>
+        <v>0.5242408207605673</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.11010679286735</v>
+        <v>-0.9839025370695973</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.3084877142912</v>
+        <v>2.384210267769851</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544785</v>
+        <v>3.798811195544783</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.15809057693509</v>
+        <v>-6.031886321137338</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4921533937076217</v>
+        <v>0.5426350960267223</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.11010679286735</v>
+        <v>-0.9839025370695973</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.289681973074996</v>
+        <v>2.365404526553647</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712296</v>
+        <v>3.797691308712294</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.91766008013023</v>
+        <v>-5.791455824332478</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.590068669054443</v>
+        <v>0.6405503713735441</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.8696762960624898</v>
+        <v>-0.743472040264737</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.435683347782789</v>
+        <v>2.51140590126144</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837688</v>
+        <v>3.821589933837686</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.845417511959035</v>
+        <v>-5.719213256161283</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6228950101577411</v>
+        <v>0.6733767124768422</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.8696762960624898</v>
+        <v>-0.743472040264737</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.439612661617609</v>
+        <v>2.515335215096261</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349969</v>
+        <v>3.822323422349967</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.72947766233385</v>
+        <v>-5.603273406536098</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6699495339251551</v>
+        <v>0.7204312362442562</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.7928545650463659</v>
+        <v>-0.6666503092486131</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.486384284144624</v>
+        <v>2.562106837623275</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972343</v>
+        <v>3.848613050972341</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.486822073910687</v>
+        <v>-5.360617818112935</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7640098405144138</v>
+        <v>0.8144915428335149</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.7928545650463659</v>
+        <v>-0.6666503092486131</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.483382355364617</v>
+        <v>2.559104908843269</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145942</v>
+        <v>3.81866537614594</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.35380488610079</v>
+        <v>-5.192978179561631</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8187957526489869</v>
+        <v>0.8831264352646504</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.7474420181111837</v>
+        <v>-0.6022293995556918</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.51220892053634</v>
+        <v>2.599336491669635</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009954</v>
+        <v>3.843270952009952</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.154556256195981</v>
+        <v>-4.993729549656822</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9143893874127338</v>
+        <v>0.9787200700283973</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.7474420181111837</v>
+        <v>-0.6022293995556918</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.528103103338164</v>
+        <v>2.615230674471459</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966262</v>
+        <v>3.845043810966259</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.995041152676611</v>
+        <v>-4.834214446137453</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9793412732607836</v>
+        <v>1.043671955876447</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.5879269145918138</v>
+        <v>-0.4427142960363218</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.624958009890087</v>
+        <v>2.712085581023382</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046999</v>
+        <v>3.791269976046996</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.850369007576874</v>
+        <v>-4.689542301037715</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.047298233862118</v>
+        <v>1.111628916477782</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.4432547694920764</v>
+        <v>-0.2980421509365844</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.72184939951137</v>
+        <v>2.808976970644665</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412106</v>
+        <v>3.735835647412103</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.910243834934566</v>
+        <v>-4.749417128395407</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.009385794320467</v>
+        <v>1.073716476936131</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.5031295968497684</v>
+        <v>-0.3579169782942765</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.67196199449818</v>
+        <v>2.759089565631475</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144519</v>
+        <v>3.762643902144516</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.823444337155557</v>
+        <v>-4.662617630616399</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.066506086754637</v>
+        <v>1.1308367693703</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.5031295968497684</v>
+        <v>-0.3579169782942765</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.694362487820746</v>
+        <v>2.781490058954041</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900696</v>
+        <v>3.729142822900693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.825914043617363</v>
+        <v>-4.665087337078205</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.065590605543327</v>
+        <v>1.12992128815899</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.5055993033115747</v>
+        <v>-0.3603866847560827</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.692953065317075</v>
+        <v>2.78008063645037</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473603</v>
+        <v>3.7432166204736</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.894284229941373</v>
+        <v>-4.733457523402215</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.049249453488425</v>
+        <v>1.113580136104088</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.4963236042753597</v>
+        <v>-0.3511109857198678</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.709525407213506</v>
+        <v>2.796652978346801</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978372</v>
+        <v>3.714175563978369</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.772867800314897</v>
+        <v>-4.612041093775739</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.088252733970907</v>
+        <v>1.15258341658657</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.4963236042753597</v>
+        <v>-0.3511109857198678</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.699962115845397</v>
+        <v>2.787089686978692</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887706</v>
+        <v>3.710903155887703</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.803860959643602</v>
+        <v>-4.643034253104444</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9005650352798114</v>
+        <v>0.9648957178954745</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.4963236042753597</v>
+        <v>-0.3511109857198678</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.524671680885784</v>
+        <v>2.611799252019079</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675905</v>
+        <v>3.746038950675901</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.628386699851132</v>
+        <v>-4.467559993311975</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.975321971188587</v>
+        <v>1.03965265380425</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.4963236042753597</v>
+        <v>-0.3511109857198678</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.529238912877572</v>
+        <v>2.616366484010867</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695449</v>
+        <v>3.765020747695447</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.739322952492381</v>
+        <v>-4.578496245953223</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9066894988932945</v>
+        <v>0.9710201815089576</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.4963236042753597</v>
+        <v>-0.3511109857198678</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.504980941638779</v>
+        <v>2.592108512772074</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581294</v>
+        <v>3.773206721581292</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.942349530035615</v>
+        <v>-4.781522823496457</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8286102530959067</v>
+        <v>0.8929409357115698</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.6993501818185931</v>
+        <v>-0.5541375632631012</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.386296380332744</v>
+        <v>2.47342395146604</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734163</v>
+        <v>3.784340376734161</v>
       </c>
       <c r="C1942" t="n">
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.784423931100322</v>
+        <v>-4.623597224561164</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9019528791021563</v>
+        <v>0.9662835617178196</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.6993501818185931</v>
+        <v>-0.5541375632631012</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.396468766764877</v>
+        <v>2.483596337898172</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869463822123</v>
+        <v>3.786946382212297</v>
       </c>
       <c r="C1943" t="n">
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.93274518491145</v>
+        <v>-4.771918478372292</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8375706481515652</v>
+        <v>0.9019013307672283</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.6993501818185931</v>
+        <v>-0.5541375632631012</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.391415037338737</v>
+        <v>2.478542608472032</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786047</v>
+        <v>3.752023923786044</v>
       </c>
       <c r="C1944" t="n">
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.933928269562511</v>
+        <v>-4.773101563023353</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8288731897356665</v>
+        <v>0.8932038723513296</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.7049932302851046</v>
+        <v>-0.5597806117296127</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.379804983703356</v>
+        <v>2.466932554836651</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273192</v>
+        <v>3.753567590273189</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.810800562568428</v>
+        <v>-4.64997385602927</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8786761455664012</v>
+        <v>0.9430068281820645</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.7049932302851046</v>
+        <v>-0.5597806117296127</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.380356856736457</v>
+        <v>2.467484427869752</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279502</v>
+        <v>3.733387025279498</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.717990081117568</v>
+        <v>-4.55716337457841</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8450730300381109</v>
+        <v>0.909403712653774</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.6121827488342453</v>
+        <v>-0.4669701302787533</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.365315837498339</v>
+        <v>2.452443408631634</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030429</v>
+        <v>3.748282241030426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.669427028896538</v>
+        <v>-4.50860032235738</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8663717268511235</v>
+        <v>0.9307024094667868</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.5636196966132151</v>
+        <v>-0.4184070780577231</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.396327144755557</v>
+        <v>2.483454715888853</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942741</v>
+        <v>3.721073619942738</v>
       </c>
       <c r="C1948" t="n">
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.556755810660288</v>
+        <v>-4.39592910412113</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9065159226573467</v>
+        <v>0.9708466052730098</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.4509484783769649</v>
+        <v>-0.3057358598214729</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.45900558420903</v>
+        <v>2.546133155342326</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268539</v>
+        <v>3.743044028268535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.444378809477615</v>
+        <v>-4.283552102938457</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9569580189610831</v>
+        <v>1.021288701576746</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.4509484783769649</v>
+        <v>-0.3057358598214729</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.464496880039698</v>
+        <v>2.551624451172993</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968865</v>
+        <v>3.689594264968861</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.642613378364346</v>
+        <v>-4.481786671825188</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8891613931749298</v>
+        <v>0.9534920757905929</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.6491830472636955</v>
+        <v>-0.5039704287082035</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.357053340476198</v>
+        <v>2.444180911609493</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175325</v>
+        <v>3.643066046175321</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.725614659389625</v>
+        <v>-4.564787952850467</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6943166007654715</v>
+        <v>0.7586472833811346</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.6677539317908692</v>
+        <v>-0.5225413132353773</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.184266529760547</v>
+        <v>2.271394100893843</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199272</v>
+        <v>3.682712735199268</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.566420387333048</v>
+        <v>-4.40559368079389</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8781439703073077</v>
+        <v>0.9424746529229711</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.6677539317908692</v>
+        <v>-0.5225413132353773</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.304416190479753</v>
+        <v>2.391543761613048</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660771</v>
+        <v>3.733008865660768</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.653018970314151</v>
+        <v>-4.492192263774993</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8580175632171896</v>
+        <v>0.9223482458328527</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.6677539317908692</v>
+        <v>-0.5225413132353773</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.318929216582076</v>
+        <v>2.406056787715371</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383427</v>
+        <v>3.741170494383423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.614635307756</v>
+        <v>-4.453808601216842</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8707904695828188</v>
+        <v>0.9351211521984819</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.629370269232718</v>
+        <v>-0.4841576506772262</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.339378855459335</v>
+        <v>2.42650642659263</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002488</v>
+        <v>3.751143622002484</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.437518977720834</v>
+        <v>-4.276692271181676</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.938366030442187</v>
+        <v>1.00269671305785</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.629370269232718</v>
+        <v>-0.4841576506772262</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.336107884304637</v>
+        <v>2.423235455437933</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263905</v>
+        <v>3.741324873263902</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.40781685374454</v>
+        <v>-4.246990147205382</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9509302717946175</v>
+        <v>1.015260954410281</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.6338403944480313</v>
+        <v>-0.4886277758925395</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.334109200937363</v>
+        <v>2.421236772070658</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.75072580148124</v>
+        <v>3.750725801481236</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.228441432505773</v>
+        <v>-4.067614725966615</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.016467415596539</v>
+        <v>1.080798098212202</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.4770636362773126</v>
+        <v>-0.3318510177218209</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.421962231146208</v>
+        <v>2.509089802279503</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452235</v>
+        <v>3.716988143452231</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.273455646026379</v>
+        <v>-4.112628939487221</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9792691855198861</v>
+        <v>1.043599868135549</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.5074125315919172</v>
+        <v>-0.3621999130364255</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.384560349289035</v>
+        <v>2.47168792042233</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,45 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.526277317971208</v>
+        <v>3.737023032979537</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.540460156298814</v>
+        <v>-4.379633449759656</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8781589437498578</v>
+        <v>0.9424896263655211</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.7017755696348658</v>
+        <v>-0.556562951079374</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.273634088802212</v>
+        <v>2.360761659935507</v>
+      </c>
+    </row>
+    <row r="1960">
+      <c r="A1960" s="2" t="n">
+        <v>45422</v>
+      </c>
+      <c r="B1960" t="n">
+        <v>3.530416653950684</v>
+      </c>
+      <c r="C1960" t="n">
+        <v>2.627699693788578</v>
+      </c>
+      <c r="D1960" t="n">
+        <v>-4.379633449759656</v>
+      </c>
+      <c r="E1960" t="n">
+        <v>0.9424896263655211</v>
+      </c>
+      <c r="F1960" t="n">
+        <v>-0.556562951079374</v>
+      </c>
+      <c r="G1960" t="n">
+        <v>2.620763490774946</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240510.xlsx
+++ b/tame_output/ON/bt/strategyON_20240510.xlsx
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.2%</t>
+          <t>-79.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>114.0%</t>
+          <t>113.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>92.5%</t>
+          <t>91.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.0%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.9%</t>
+          <t>-76.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>94.7%</t>
+          <t>94.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>441.4%</t>
+          <t>441.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-599.5%</t>
+          <t>-615.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.4%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-35.1%</t>
+          <t>-40.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-282.0%</t>
+          <t>-288.4%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-32.2%</t>
+          <t>-33.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.7%</t>
+          <t>69.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-27.0%</t>
+          <t>-28.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>37.2%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-154.5%</t>
+          <t>-157.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-279.6%</t>
+          <t>-294.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776679</v>
+        <v>3.50044609677668</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.275880984781383</v>
+        <v>-9.402085240579135</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.5621424004446181</v>
+        <v>-0.6126241027637191</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.573879342692381</v>
+        <v>-2.700083598490133</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.604238812166254</v>
+        <v>1.528516258687603</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.195811189243578</v>
+        <v>-9.32201544504133</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.5307476610087392</v>
+        <v>-0.5812293633278403</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.493809547154577</v>
+        <v>-2.620013802952329</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.651647510709694</v>
+        <v>1.575924957231042</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.962329967013979</v>
+        <v>-9.088534222811731</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.4294307432790472</v>
+        <v>-0.4799124455981483</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.260328324924978</v>
+        <v>-2.386532580722731</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.799660672885305</v>
+        <v>1.723938119406654</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.782621436870105</v>
+        <v>-8.908825692667858</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.3604395415344568</v>
+        <v>-0.4109212438535579</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.203156820762282</v>
+        <v>-2.329361076560035</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.831071365069963</v>
+        <v>1.755348811591312</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.650345963239218</v>
+        <v>-8.77655021903697</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.3121618653350748</v>
+        <v>-0.3626435676541759</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.070881347131396</v>
+        <v>-2.197085602929148</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.905804135995522</v>
+        <v>1.830081582516871</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.459746288566064</v>
+        <v>-8.585950544363817</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.2331069347781769</v>
+        <v>-0.283588637097278</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.880281672458243</v>
+        <v>-2.006485928255995</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.022979001487051</v>
+        <v>1.947256448008399</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.210746489882483</v>
+        <v>-8.336950745680236</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.1206006740810857</v>
+        <v>-0.1710823764001868</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.880281672458243</v>
+        <v>-2.006485928255995</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.035885342710709</v>
+        <v>1.960162789232058</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.316336479655588</v>
+        <v>-8.44254073545334</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.2908125995895463</v>
+        <v>-0.341294301908647</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.985871662231347</v>
+        <v>-2.1120759180291</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.844555419247628</v>
+        <v>1.768832865768977</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.335071381774185</v>
+        <v>-8.461275637571937</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.2497622185598987</v>
+        <v>-0.3002439208789998</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.985871662231347</v>
+        <v>-2.1120759180291</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.893099761124714</v>
+        <v>1.817377207646063</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.187131340366586</v>
+        <v>-8.313335596164338</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.3104651246850265</v>
+        <v>-0.3609468270041276</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.96555074632279</v>
+        <v>-2.091755002120542</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.785413387981681</v>
+        <v>1.70969083450303</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.162902703977613</v>
+        <v>-8.289106959775365</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.3094876563829159</v>
+        <v>-0.3599693587020165</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.941322109933818</v>
+        <v>-2.06752636573157</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.791236583561587</v>
+        <v>1.715514030082935</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.119354297206922</v>
+        <v>-8.245558553004674</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.2990289057697324</v>
+        <v>-0.3495106080888331</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.941322109933818</v>
+        <v>-2.06752636573157</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.784275971466494</v>
+        <v>1.708553417987842</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.877205903753064</v>
+        <v>-8.003410159550816</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.1877071940070461</v>
+        <v>-0.2381888963261467</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.941322109933818</v>
+        <v>-2.06752636573157</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.798738325847637</v>
+        <v>1.723015772368985</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.813976531984715</v>
+        <v>-7.940180787782467</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.1678833248405116</v>
+        <v>-0.2183650271596127</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.941322109933818</v>
+        <v>-2.06752636573157</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.793270446306832</v>
+        <v>1.71754789282818</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.690685397167584</v>
+        <v>-7.816889652965337</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.1210687769030825</v>
+        <v>-0.1715504792221831</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.818030975116687</v>
+        <v>-1.94423523091444</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.864743221207687</v>
+        <v>1.789020667729035</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.669536198264141</v>
+        <v>-7.795740454061893</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.1049081191043797</v>
+        <v>-0.1553898214234808</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.796881776213244</v>
+        <v>-1.923086032010997</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.885133718787078</v>
+        <v>1.809411165308426</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.425770756280697</v>
+        <v>-7.551975012078449</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.01162123396395165</v>
+        <v>-0.0621029362830523</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.796881776213244</v>
+        <v>-1.923086032010997</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.880914427134128</v>
+        <v>1.805191873655477</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.161742689087436</v>
+        <v>-7.287946944885189</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.09611430683336852</v>
+        <v>0.04563260451426787</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.59501637739729</v>
+        <v>-1.721220633195043</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.004157980343717</v>
+        <v>1.928435426865065</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.911892295138362</v>
+        <v>-7.038096550936114</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.1887965393967006</v>
+        <v>0.1383148370776</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.59501637739729</v>
+        <v>-1.721220633195043</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.996900055327419</v>
+        <v>1.921177501848767</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.73600020267093</v>
+        <v>-6.862204458468682</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.2627524999043223</v>
+        <v>0.2122707975852212</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.59501637739729</v>
+        <v>-1.721220633195043</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.000499178848067</v>
+        <v>1.924776625369416</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.564553739648466</v>
+        <v>-6.690757995446218</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.3446585911678612</v>
+        <v>0.2941768888487606</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.423569914374827</v>
+        <v>-1.54977417017258</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.116694562716099</v>
+        <v>2.040972009237448</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.339520739979643</v>
+        <v>-6.465724995777395</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.4336922686516873</v>
+        <v>0.3832105663325867</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.198536914706004</v>
+        <v>-1.324741170503757</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.25073484013369</v>
+        <v>2.175012286655038</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.124886362343236</v>
+        <v>-6.251090618140989</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5242408207605673</v>
+        <v>0.4737591184414667</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.9839025370695973</v>
+        <v>-1.11010679286735</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.384210267769851</v>
+        <v>2.3084877142912</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.031886321137338</v>
+        <v>-6.15809057693509</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5426350960267223</v>
+        <v>0.4921533937076217</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.9839025370695973</v>
+        <v>-1.11010679286735</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.365404526553647</v>
+        <v>2.289681973074996</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.791455824332478</v>
+        <v>-5.91766008013023</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6405503713735441</v>
+        <v>0.590068669054443</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.743472040264737</v>
+        <v>-0.8696762960624898</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.51140590126144</v>
+        <v>2.435683347782789</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.719213256161283</v>
+        <v>-5.845417511959035</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6733767124768422</v>
+        <v>0.6228950101577411</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.743472040264737</v>
+        <v>-0.8696762960624898</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.515335215096261</v>
+        <v>2.439612661617609</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.603273406536098</v>
+        <v>-5.72947766233385</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7204312362442562</v>
+        <v>0.6699495339251551</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.6666503092486131</v>
+        <v>-0.7928545650463659</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.562106837623275</v>
+        <v>2.486384284144624</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.360617818112935</v>
+        <v>-5.486822073910687</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8144915428335149</v>
+        <v>0.7640098405144138</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.6666503092486131</v>
+        <v>-0.7928545650463659</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.559104908843269</v>
+        <v>2.483382355364617</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.81866537614594</v>
+        <v>3.818665376145941</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.192978179561631</v>
+        <v>-5.35380488610079</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8831264352646504</v>
+        <v>0.8187957526489869</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.6022293995556918</v>
+        <v>-0.7474420181111837</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.599336491669635</v>
+        <v>2.51220892053634</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009952</v>
+        <v>3.843270952009953</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.993729549656822</v>
+        <v>-5.154556256195981</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9787200700283973</v>
+        <v>0.9143893874127338</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.6022293995556918</v>
+        <v>-0.7474420181111837</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.615230674471459</v>
+        <v>2.528103103338164</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966259</v>
+        <v>3.84504381096626</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.834214446137453</v>
+        <v>-4.995041152676611</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.043671955876447</v>
+        <v>0.9793412732607836</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.4427142960363218</v>
+        <v>-0.5879269145918138</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.712085581023382</v>
+        <v>2.624958009890087</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046996</v>
+        <v>3.791269976046997</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.689542301037715</v>
+        <v>-4.850369007576874</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.111628916477782</v>
+        <v>1.047298233862118</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.2980421509365844</v>
+        <v>-0.4432547694920764</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.808976970644665</v>
+        <v>2.72184939951137</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412103</v>
+        <v>3.735835647412104</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.749417128395407</v>
+        <v>-4.910243834934566</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.073716476936131</v>
+        <v>1.009385794320467</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.3579169782942765</v>
+        <v>-0.5031295968497684</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.759089565631475</v>
+        <v>2.67196199449818</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144516</v>
+        <v>3.762643902144517</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.662617630616399</v>
+        <v>-4.823444337155557</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.1308367693703</v>
+        <v>1.066506086754637</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.3579169782942765</v>
+        <v>-0.5031295968497684</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.781490058954041</v>
+        <v>2.694362487820746</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900693</v>
+        <v>3.729142822900695</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.665087337078205</v>
+        <v>-4.825914043617363</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.12992128815899</v>
+        <v>1.065590605543327</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.3603866847560827</v>
+        <v>-0.5055993033115747</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.78008063645037</v>
+        <v>2.692953065317075</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432166204736</v>
+        <v>3.743216620473602</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.733457523402215</v>
+        <v>-4.894284229941373</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.113580136104088</v>
+        <v>1.049249453488425</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.3511109857198678</v>
+        <v>-0.4963236042753597</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.796652978346801</v>
+        <v>2.709525407213506</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978369</v>
+        <v>3.714175563978371</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.612041093775739</v>
+        <v>-4.772867800314897</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.15258341658657</v>
+        <v>1.088252733970907</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.3511109857198678</v>
+        <v>-0.4963236042753597</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.787089686978692</v>
+        <v>2.699962115845397</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887703</v>
+        <v>3.710903155887705</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.643034253104444</v>
+        <v>-4.803860959643602</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9648957178954745</v>
+        <v>0.9005650352798114</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.3511109857198678</v>
+        <v>-0.4963236042753597</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.611799252019079</v>
+        <v>2.524671680885784</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675901</v>
+        <v>3.746038950675903</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.467559993311975</v>
+        <v>-4.628386699851132</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.03965265380425</v>
+        <v>0.975321971188587</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.3511109857198678</v>
+        <v>-0.4963236042753597</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.616366484010867</v>
+        <v>2.529238912877572</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695447</v>
+        <v>3.765020747695448</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.578496245953223</v>
+        <v>-4.739322952492381</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9710201815089576</v>
+        <v>0.9066894988932945</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.3511109857198678</v>
+        <v>-0.4963236042753597</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.592108512772074</v>
+        <v>2.504980941638779</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581292</v>
+        <v>3.773206721581293</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.781522823496457</v>
+        <v>-4.942349530035615</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8929409357115698</v>
+        <v>0.8286102530959067</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.5541375632631012</v>
+        <v>-0.6993501818185931</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.47342395146604</v>
+        <v>2.386296380332744</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734161</v>
+        <v>3.784340376734162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.623597224561164</v>
+        <v>-4.784423931100322</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9662835617178196</v>
+        <v>0.9019528791021563</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.5541375632631012</v>
+        <v>-0.6993501818185931</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.483596337898172</v>
+        <v>2.396468766764877</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212297</v>
+        <v>3.786946382212299</v>
       </c>
       <c r="C1943" t="n">
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.771918478372292</v>
+        <v>-4.93274518491145</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9019013307672283</v>
+        <v>0.8375706481515652</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.5541375632631012</v>
+        <v>-0.6993501818185931</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.478542608472032</v>
+        <v>2.391415037338737</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786044</v>
+        <v>3.752023923786046</v>
       </c>
       <c r="C1944" t="n">
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.773101563023353</v>
+        <v>-4.933928269562511</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8932038723513296</v>
+        <v>0.8288731897356665</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.5597806117296127</v>
+        <v>-0.7049932302851046</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.466932554836651</v>
+        <v>2.379804983703356</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273189</v>
+        <v>3.753567590273191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.64997385602927</v>
+        <v>-4.810800562568428</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9430068281820645</v>
+        <v>0.8786761455664012</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.5597806117296127</v>
+        <v>-0.7049932302851046</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.467484427869752</v>
+        <v>2.380356856736457</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279498</v>
+        <v>3.7333870252795</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.55716337457841</v>
+        <v>-4.717990081117568</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.909403712653774</v>
+        <v>0.8450730300381109</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.4669701302787533</v>
+        <v>-0.6121827488342453</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.452443408631634</v>
+        <v>2.365315837498339</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030426</v>
+        <v>3.748282241030427</v>
       </c>
       <c r="C1947" t="n">
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.50860032235738</v>
+        <v>-4.669427028896538</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9307024094667868</v>
+        <v>0.8663717268511235</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.4184070780577231</v>
+        <v>-0.5636196966132151</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.483454715888853</v>
+        <v>2.396327144755557</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942738</v>
+        <v>3.721073619942739</v>
       </c>
       <c r="C1948" t="n">
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.39592910412113</v>
+        <v>-4.556755810660288</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9708466052730098</v>
+        <v>0.9065159226573467</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.3057358598214729</v>
+        <v>-0.4509484783769649</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.546133155342326</v>
+        <v>2.45900558420903</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268535</v>
+        <v>3.743044028268537</v>
       </c>
       <c r="C1949" t="n">
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.283552102938457</v>
+        <v>-4.444378809477615</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.021288701576746</v>
+        <v>0.9569580189610831</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.3057358598214729</v>
+        <v>-0.4509484783769649</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.551624451172993</v>
+        <v>2.464496880039698</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968861</v>
+        <v>3.689594264968863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.481786671825188</v>
+        <v>-4.642613378364346</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9534920757905929</v>
+        <v>0.8891613931749298</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.5039704287082035</v>
+        <v>-0.6491830472636955</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.444180911609493</v>
+        <v>2.357053340476198</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175321</v>
+        <v>3.643066046175323</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.564787952850467</v>
+        <v>-4.725614659389625</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7586472833811346</v>
+        <v>0.6943166007654715</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.5225413132353773</v>
+        <v>-0.6677539317908692</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.271394100893843</v>
+        <v>2.184266529760547</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199268</v>
+        <v>3.68271273519927</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.40559368079389</v>
+        <v>-4.566420387333048</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9424746529229711</v>
+        <v>0.8781439703073077</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.5225413132353773</v>
+        <v>-0.6677539317908692</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.391543761613048</v>
+        <v>2.304416190479753</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660768</v>
+        <v>3.73300886566077</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.492192263774993</v>
+        <v>-4.653018970314151</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9223482458328527</v>
+        <v>0.8580175632171896</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.5225413132353773</v>
+        <v>-0.6677539317908692</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.406056787715371</v>
+        <v>2.318929216582076</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383423</v>
+        <v>3.741170494383425</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.453808601216842</v>
+        <v>-4.614635307756</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9351211521984819</v>
+        <v>0.8707904695828188</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.4841576506772262</v>
+        <v>-0.629370269232718</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.42650642659263</v>
+        <v>2.339378855459335</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002484</v>
+        <v>3.751143622002486</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.276692271181676</v>
+        <v>-4.437518977720834</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.00269671305785</v>
+        <v>0.938366030442187</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.4841576506772262</v>
+        <v>-0.629370269232718</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.423235455437933</v>
+        <v>2.336107884304637</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263902</v>
+        <v>3.741324873263904</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.246990147205382</v>
+        <v>-4.40781685374454</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.015260954410281</v>
+        <v>0.9509302717946175</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.4886277758925395</v>
+        <v>-0.6338403944480313</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.421236772070658</v>
+        <v>2.334109200937363</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481236</v>
+        <v>3.750725801481238</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.067614725966615</v>
+        <v>-4.228441432505773</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.080798098212202</v>
+        <v>1.016467415596539</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.3318510177218209</v>
+        <v>-0.4770636362773126</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.509089802279503</v>
+        <v>2.421962231146208</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452231</v>
+        <v>3.716988143452233</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.112628939487221</v>
+        <v>-4.273455646026379</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.043599868135549</v>
+        <v>0.9792691855198861</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.3621999130364255</v>
+        <v>-0.5074125315919172</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.47168792042233</v>
+        <v>2.384560349289035</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979537</v>
+        <v>3.73702303297954</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.379633449759656</v>
+        <v>-4.540460156298814</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9424896263655211</v>
+        <v>0.8781589437498578</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.556562951079374</v>
+        <v>-0.7017755696348658</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.360761659935507</v>
+        <v>2.273634088802212</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,19 +46625,19 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.530416653950684</v>
+        <v>3.530416653950686</v>
       </c>
       <c r="C1960" t="n">
         <v>2.627699693788578</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.379633449759656</v>
+        <v>-4.540460156298814</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9424896263655211</v>
+        <v>0.8781589437498578</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.556562951079374</v>
+        <v>-0.7017755696348658</v>
       </c>
       <c r="G1960" t="n">
         <v>2.620763490774946</v>

--- a/tame_output/ON/bt/strategyON_20240510.xlsx
+++ b/tame_output/ON/bt/strategyON_20240510.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>61.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -671,17 +671,17 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.1%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>48.8%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -824,22 +824,22 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-10.3%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.2%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>42.1%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-48.9%</t>
+          <t>-35.0%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.8%</t>
+          <t>-79.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>113.7%</t>
+          <t>113.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>133.9%</t>
+          <t>133.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.8%</t>
+          <t>92.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-55.8%</t>
+          <t>-55.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.5%</t>
+          <t>-75.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>94.4%</t>
+          <t>94.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>441.1%</t>
+          <t>444.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.3%</t>
+          <t>-9.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-615.6%</t>
+          <t>-604.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-40.7%</t>
+          <t>-40.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-288.4%</t>
+          <t>-283.9%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-33.9%</t>
+          <t>-32.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.4%</t>
+          <t>69.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.49</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>70.5%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-34.4%</t>
+          <t>-34.2%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-28.8%</t>
+          <t>-26.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-157.1%</t>
+          <t>-153.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-294.2%</t>
+          <t>-281.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>42.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,27 +1466,27 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-31.3%</t>
+          <t>-31.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1496,17 +1496,17 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.3%</t>
+          <t>-16.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-183.9%</t>
+          <t>-170.1%</t>
         </is>
       </c>
     </row>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297753</v>
+        <v>3.458100091297752</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.44775050131762</v>
+        <v>3.447750501317619</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.468790384536863</v>
+        <v>-9.44235447177735</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.6722673131904568</v>
+        <v>-0.6616929480866514</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.967351536711524</v>
+        <v>-1.94091562395201</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.935194342911122</v>
+        <v>1.95105589056683</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737174</v>
+        <v>3.503515506737173</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.828320707040865</v>
+        <v>-9.801884794281351</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.8107291388940072</v>
+        <v>-0.8001547737902017</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.967351536711524</v>
+        <v>-1.94091562395201</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.940544646209172</v>
+        <v>1.956406193864881</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.15472073570588</v>
+        <v>-10.12828482294636</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.9333731304028352</v>
+        <v>-0.9227987652990293</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.293751565376537</v>
+        <v>-2.267315652617023</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.752620648967342</v>
+        <v>1.76848219662305</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.37386970378008</v>
+        <v>-10.34743379102056</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.017990967010745</v>
+        <v>-1.00741660190694</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.512900533450734</v>
+        <v>-2.48646462069122</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.624173018744592</v>
+        <v>1.640034566400301</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.37017877882366</v>
+        <v>-10.34374286606415</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.016514597028181</v>
+        <v>-1.005940231924375</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.512900533450734</v>
+        <v>-2.48646462069122</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.624173018744592</v>
+        <v>1.640034566400301</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.57443695415353</v>
+        <v>-10.54800104139401</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.092704670041484</v>
+        <v>-1.082130304937678</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.640539478064723</v>
+        <v>-2.614103565305209</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.553102849094841</v>
+        <v>1.56896439675055</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.79247472578471</v>
+        <v>-10.76603881302519</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.175437224209519</v>
+        <v>-1.164862859105714</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.815310246160622</v>
+        <v>-2.788874333401108</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.452722942721738</v>
+        <v>1.468584490377446</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.71900489411726</v>
+        <v>-10.69256898135774</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.130677590049118</v>
+        <v>-1.120103224945312</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.741840414493173</v>
+        <v>-2.715404501733659</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.512176543215628</v>
+        <v>1.528038090871337</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.8941293115038</v>
+        <v>-10.86769339874429</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.186172136256219</v>
+        <v>-1.175597771152413</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.916964831879717</v>
+        <v>-2.890528919120203</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.421657113531219</v>
+        <v>1.437518661186927</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.12858140551829</v>
+        <v>-11.10214549275878</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.287172138763611</v>
+        <v>-1.276597773659805</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.916964831879717</v>
+        <v>-2.890528919120203</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.414437948629623</v>
+        <v>1.430299496285331</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.41638525005553</v>
+        <v>-11.38994933729601</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.408965867352482</v>
+        <v>-1.398391502248677</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.204768676416955</v>
+        <v>-3.178332763657441</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.235083451133304</v>
+        <v>1.250944998789012</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.64620969721935</v>
+        <v>-11.61977378445984</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.499779856379456</v>
+        <v>-1.48920549127565</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.367416213487116</v>
+        <v>-3.340980300727602</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.138610718729764</v>
+        <v>1.154472266385472</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.87823861695562</v>
+        <v>-11.8518027041961</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.589897695644846</v>
+        <v>-1.579323330541041</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.429428910675539</v>
+        <v>-3.402992997916025</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.104096829045825</v>
+        <v>1.119958376701533</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.8262231029868</v>
+        <v>-11.79978719022729</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.56510115437092</v>
+        <v>-1.554526789267114</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.429428910675539</v>
+        <v>-3.402992997916025</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.108087164732225</v>
+        <v>1.123948712387933</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.96789494471092</v>
+        <v>-11.94145903195141</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.62324511795931</v>
+        <v>-1.612670752855504</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.429428910675539</v>
+        <v>-3.402992997916025</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.106611937833484</v>
+        <v>1.122473485489192</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.91830410028609</v>
+        <v>-11.89186818752657</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.588355370024504</v>
+        <v>-1.577781004920698</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.379838066250705</v>
+        <v>-3.353402153491191</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.151419854653256</v>
+        <v>1.167281402308964</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.71915199304899</v>
+        <v>-11.69271608028948</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.521745660776347</v>
+        <v>-1.511171295672541</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.214515540300892</v>
+        <v>-3.188079627541378</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.237562236576461</v>
+        <v>1.25342378423217</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.49330684032958</v>
+        <v>-11.46687092757006</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.421828526652373</v>
+        <v>-1.411254161548568</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.172588864713728</v>
+        <v>-3.146152951954214</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.272297314964968</v>
+        <v>1.288158862620676</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.36872818399199</v>
+        <v>-11.34229227123247</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.370857919561278</v>
+        <v>-1.360283554457472</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.172588864713728</v>
+        <v>-3.146152951954214</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.273436459521027</v>
+        <v>1.289298007176735</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.42162347203627</v>
+        <v>-11.39518755927676</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.389382260616885</v>
+        <v>-1.37880789551308</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.167633518625282</v>
+        <v>-3.141197605865768</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.279043441336202</v>
+        <v>1.294904988991911</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.13771474110752</v>
+        <v>-11.11127882834801</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.270085064006749</v>
+        <v>-1.259510698902943</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.167633518625282</v>
+        <v>-3.141197605865768</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.284777145574839</v>
+        <v>1.300638693230547</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.06634834849788</v>
+        <v>-11.03991243573836</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.251275769356755</v>
+        <v>-1.24070140425295</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.096267126015634</v>
+        <v>-3.069831213256121</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.317859718746762</v>
+        <v>1.33372126640247</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.80251148129381</v>
+        <v>-10.77607556853429</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.155624503788034</v>
+        <v>-1.145050138684229</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.096267126015634</v>
+        <v>-3.069831213256121</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.307976237433855</v>
+        <v>1.323837785089563</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.53526968042541</v>
+        <v>-10.50883376766589</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.05056234394005</v>
+        <v>-1.039987978836244</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.096267126015634</v>
+        <v>-3.069831213256121</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.306141676934481</v>
+        <v>1.322003224590189</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.43736264174892</v>
+        <v>-10.4109267289894</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.011699843442914</v>
+        <v>-1.001125478339108</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.028281376155078</v>
+        <v>-3.001845463395564</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.346632811877354</v>
+        <v>1.362494359533062</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.41340910077296</v>
+        <v>-10.38697318801345</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.001449920907037</v>
+        <v>-0.9908755558032314</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.00432783517912</v>
+        <v>-2.977891922419607</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.361673442608422</v>
+        <v>1.37753499026413</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.14934916245016</v>
+        <v>-10.12291324969065</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.9090862617396702</v>
+        <v>-0.8985118966358652</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.740267896856324</v>
+        <v>-2.713831984096811</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.506849089440348</v>
+        <v>1.522710637096056</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.442269538945325</v>
+        <v>-9.415833626185812</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.6290414459980367</v>
+        <v>-0.6184670808942312</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.740267896856324</v>
+        <v>-2.713831984096811</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.504062055780047</v>
+        <v>1.519923603435755</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.402085240579135</v>
+        <v>-9.375649327819621</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.6126241027637191</v>
+        <v>-0.6020497376599137</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.700083598490133</v>
+        <v>-2.67364768573062</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.528516258687603</v>
+        <v>1.544377806343311</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.32201544504133</v>
+        <v>-9.295579532281817</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.5812293633278403</v>
+        <v>-0.5706549982240348</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.620013802952329</v>
+        <v>-2.593577890192816</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.575924957231042</v>
+        <v>1.59178650488675</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.088534222811731</v>
+        <v>-9.062098310052217</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.4799124455981483</v>
+        <v>-0.4693380804943428</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.386532580722731</v>
+        <v>-2.360096667963217</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.723938119406654</v>
+        <v>1.739799667062362</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.908825692667858</v>
+        <v>-8.882389779908344</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.4109212438535579</v>
+        <v>-0.4003468787497524</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.329361076560035</v>
+        <v>-2.302925163800521</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.755348811591312</v>
+        <v>1.77121035924702</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.77655021903697</v>
+        <v>-8.750114306277457</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.3626435676541759</v>
+        <v>-0.3520692025503704</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.197085602929148</v>
+        <v>-2.170649690169635</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.830081582516871</v>
+        <v>1.845943130172579</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.585950544363817</v>
+        <v>-8.559514631604303</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.283588637097278</v>
+        <v>-0.2730142719934725</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.006485928255995</v>
+        <v>-1.980050015496482</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.947256448008399</v>
+        <v>1.963117995664107</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.336950745680236</v>
+        <v>-8.310514832920722</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.1710823764001868</v>
+        <v>-0.1605080112963813</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.006485928255995</v>
+        <v>-1.980050015496482</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.960162789232058</v>
+        <v>1.976024336887766</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.44254073545334</v>
+        <v>-8.416104822693827</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.341294301908647</v>
+        <v>-0.3307199368048419</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.1120759180291</v>
+        <v>-2.085640005269586</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.768832865768977</v>
+        <v>1.784694413424685</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.461275637571937</v>
+        <v>-8.434839724812424</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.3002439208789998</v>
+        <v>-0.2896695557751943</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.1120759180291</v>
+        <v>-2.085640005269586</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.817377207646063</v>
+        <v>1.833238755301771</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.313335596164338</v>
+        <v>-8.286899683404824</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.3609468270041276</v>
+        <v>-0.3503724619003221</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.091755002120542</v>
+        <v>-2.065319089361029</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.70969083450303</v>
+        <v>1.725552382158738</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.289106959775365</v>
+        <v>-8.262671047015852</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.3599693587020165</v>
+        <v>-0.349394993598211</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.06752636573157</v>
+        <v>-2.041090452972057</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.715514030082935</v>
+        <v>1.731375577738643</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.245558553004674</v>
+        <v>-8.21912264024516</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.3495106080888331</v>
+        <v>-0.338936242985028</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.06752636573157</v>
+        <v>-2.041090452972057</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.708553417987842</v>
+        <v>1.72441496564355</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.003410159550816</v>
+        <v>-7.976974246791302</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.2381888963261467</v>
+        <v>-0.2276145312223417</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.06752636573157</v>
+        <v>-2.041090452972057</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.723015772368985</v>
+        <v>1.738877320024693</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.940180787782467</v>
+        <v>-7.913744875022954</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.2183650271596127</v>
+        <v>-0.2077906620558072</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.06752636573157</v>
+        <v>-2.041090452972057</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.71754789282818</v>
+        <v>1.733409440483888</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.816889652965337</v>
+        <v>-7.790453740205823</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.1715504792221831</v>
+        <v>-0.1609761141183781</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.94423523091444</v>
+        <v>-1.917799318154926</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.789020667729035</v>
+        <v>1.804882215384743</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.795740454061893</v>
+        <v>-7.76930454130238</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.1553898214234808</v>
+        <v>-0.1448154563196753</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.923086032010997</v>
+        <v>-1.896650119251483</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.809411165308426</v>
+        <v>1.825272712964134</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.551975012078449</v>
+        <v>-7.525539099318935</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.0621029362830523</v>
+        <v>-0.05152857117924681</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.923086032010997</v>
+        <v>-1.896650119251483</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.805191873655477</v>
+        <v>1.821053421311185</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.287946944885189</v>
+        <v>-7.261511032125675</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.04563260451426787</v>
+        <v>0.05620696961807337</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.721220633195043</v>
+        <v>-1.69478472043553</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.928435426865065</v>
+        <v>1.944296974520773</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.038096550936114</v>
+        <v>-7.0116606381766</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.1383148370776</v>
+        <v>0.148889202181405</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.721220633195043</v>
+        <v>-1.69478472043553</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.921177501848767</v>
+        <v>1.937039049504476</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.862204458468682</v>
+        <v>-6.835768545709168</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.2122707975852212</v>
+        <v>0.2228451626890267</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.721220633195043</v>
+        <v>-1.69478472043553</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.924776625369416</v>
+        <v>1.940638173025124</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.690757995446218</v>
+        <v>-6.664322082686705</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.2941768888487606</v>
+        <v>0.3047512539525656</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.54977417017258</v>
+        <v>-1.523338257413066</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.040972009237448</v>
+        <v>2.056833556893156</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.465724995777395</v>
+        <v>-6.439289083017882</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.3832105663325867</v>
+        <v>0.3937849314363921</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.324741170503757</v>
+        <v>-1.298305257744243</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.175012286655038</v>
+        <v>2.190873834310747</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.251090618140989</v>
+        <v>-6.224654705381475</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.4737591184414667</v>
+        <v>0.4843334835452722</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.11010679286735</v>
+        <v>-1.083670880107837</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.3084877142912</v>
+        <v>2.324349261946908</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.15809057693509</v>
+        <v>-6.131654664175577</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4921533937076217</v>
+        <v>0.5027277588114267</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.11010679286735</v>
+        <v>-1.083670880107837</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.289681973074996</v>
+        <v>2.305543520730704</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.91766008013023</v>
+        <v>-5.891224167370717</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.590068669054443</v>
+        <v>0.6006430341582485</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.8696762960624898</v>
+        <v>-0.8432403833029762</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.435683347782789</v>
+        <v>2.451544895438497</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.845417511959035</v>
+        <v>-5.818981599199522</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6228950101577411</v>
+        <v>0.6334693752615466</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.8696762960624898</v>
+        <v>-0.8432403833029762</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.439612661617609</v>
+        <v>2.455474209273317</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.72947766233385</v>
+        <v>-5.703041749574337</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6699495339251551</v>
+        <v>0.6805238990289606</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.7928545650463659</v>
+        <v>-0.7664186522868524</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.486384284144624</v>
+        <v>2.502245831800332</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.486822073910687</v>
+        <v>-5.460386161151174</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7640098405144138</v>
+        <v>0.7745842056182193</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.7928545650463659</v>
+        <v>-0.7664186522868524</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.483382355364617</v>
+        <v>2.499243903020325</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.35380488610079</v>
+        <v>-5.240365363114163</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8187957526489869</v>
+        <v>0.8641715618436376</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.7474420181111837</v>
+        <v>-0.6251988072188721</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.51220892053634</v>
+        <v>2.585554847071727</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.154556256195981</v>
+        <v>-5.041116733209354</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9143893874127338</v>
+        <v>0.9597651966073846</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.7474420181111837</v>
+        <v>-0.6251988072188721</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.528103103338164</v>
+        <v>2.60144902987355</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.995041152676611</v>
+        <v>-4.881601629689984</v>
       </c>
       <c r="E1931" t="n">
-        <v>0.9793412732607836</v>
+        <v>1.024717082455434</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.5879269145918138</v>
+        <v>-0.4656837036995022</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.624958009890087</v>
+        <v>2.698303936425474</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.850369007576874</v>
+        <v>-4.736929484590247</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.047298233862118</v>
+        <v>1.092674043056769</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.4432547694920764</v>
+        <v>-0.3210115585997648</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.72184939951137</v>
+        <v>2.795195326046757</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.910243834934566</v>
+        <v>-4.796804311947939</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.009385794320467</v>
+        <v>1.054761603515118</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.5031295968497684</v>
+        <v>-0.3808863859574569</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.67196199449818</v>
+        <v>2.745307921033567</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.823444337155557</v>
+        <v>-4.710004814168931</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.066506086754637</v>
+        <v>1.111881895949288</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.5031295968497684</v>
+        <v>-0.3808863859574569</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.694362487820746</v>
+        <v>2.767708414356133</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.825914043617363</v>
+        <v>-4.712474520630737</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.065590605543327</v>
+        <v>1.110966414737977</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.5055993033115747</v>
+        <v>-0.3833560924192631</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.692953065317075</v>
+        <v>2.766298991852462</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.894284229941373</v>
+        <v>-4.780844706954747</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.049249453488425</v>
+        <v>1.094625262683075</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.4963236042753597</v>
+        <v>-0.3740803933830481</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.709525407213506</v>
+        <v>2.782871333748893</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.772867800314897</v>
+        <v>-4.659428277328271</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.088252733970907</v>
+        <v>1.133628543165557</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.4963236042753597</v>
+        <v>-0.3740803933830481</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.699962115845397</v>
+        <v>2.773308042380784</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.803860959643602</v>
+        <v>-4.690421436656976</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9005650352798114</v>
+        <v>0.9459408444744617</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.4963236042753597</v>
+        <v>-0.3740803933830481</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.524671680885784</v>
+        <v>2.598017607421171</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.628386699851132</v>
+        <v>-4.514947176864506</v>
       </c>
       <c r="E1939" t="n">
-        <v>0.975321971188587</v>
+        <v>1.020697780383237</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.4963236042753597</v>
+        <v>-0.3740803933830481</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.529238912877572</v>
+        <v>2.602584839412958</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.739322952492381</v>
+        <v>-4.625883429505755</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9066894988932945</v>
+        <v>0.9520653080879449</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.4963236042753597</v>
+        <v>-0.3740803933830481</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.504980941638779</v>
+        <v>2.578326868174166</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.942349530035615</v>
+        <v>-4.828910007048989</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8286102530959067</v>
+        <v>0.8739860622905571</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.6993501818185931</v>
+        <v>-0.5771069709262815</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.386296380332744</v>
+        <v>2.459642306868131</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.784423931100322</v>
+        <v>-4.670984408113696</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9019528791021563</v>
+        <v>0.9473286882968068</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.6993501818185931</v>
+        <v>-0.5771069709262815</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.396468766764877</v>
+        <v>2.469814693300264</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.93274518491145</v>
+        <v>-4.819305661924824</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8375706481515652</v>
+        <v>0.8829464573462156</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.6993501818185931</v>
+        <v>-0.5771069709262815</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.391415037338737</v>
+        <v>2.464760963874124</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.933928269562511</v>
+        <v>-4.820488746575885</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8288731897356665</v>
+        <v>0.8742489989303168</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.7049932302851046</v>
+        <v>-0.582750019392793</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.379804983703356</v>
+        <v>2.453150910238743</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.810800562568428</v>
+        <v>-4.697361039581802</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.8786761455664012</v>
+        <v>0.9240519547610517</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.7049932302851046</v>
+        <v>-0.582750019392793</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.380356856736457</v>
+        <v>2.453702783271844</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.717990081117568</v>
+        <v>-4.604550558130942</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8450730300381109</v>
+        <v>0.8904488392327612</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.6121827488342453</v>
+        <v>-0.4899395379419337</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.365315837498339</v>
+        <v>2.438661764033725</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.669427028896538</v>
+        <v>-4.555987505909912</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.8663717268511235</v>
+        <v>0.9117475360457741</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.5636196966132151</v>
+        <v>-0.4413764857209035</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.396327144755557</v>
+        <v>2.469673071290944</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.556755810660288</v>
+        <v>-4.443316287673662</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.9065159226573467</v>
+        <v>0.951891731851997</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.4509484783769649</v>
+        <v>-0.3287052674846533</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.45900558420903</v>
+        <v>2.532351510744418</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.444378809477615</v>
+        <v>-4.330939286490989</v>
       </c>
       <c r="E1949" t="n">
-        <v>0.9569580189610831</v>
+        <v>1.002333828155733</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.4509484783769649</v>
+        <v>-0.3287052674846533</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.464496880039698</v>
+        <v>2.537842806575084</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.642613378364346</v>
+        <v>-4.52917385537772</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.8891613931749298</v>
+        <v>0.9345372023695802</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.6491830472636955</v>
+        <v>-0.5269398363713839</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.357053340476198</v>
+        <v>2.430399267011585</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.725614659389625</v>
+        <v>-4.612175136402999</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.6943166007654715</v>
+        <v>0.7396924099601219</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.6677539317908692</v>
+        <v>-0.5455107208985577</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.184266529760547</v>
+        <v>2.257612456295934</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.566420387333048</v>
+        <v>-4.452980864346422</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.8781439703073077</v>
+        <v>0.9235197795019583</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.6677539317908692</v>
+        <v>-0.5455107208985577</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.304416190479753</v>
+        <v>2.37776211701514</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.653018970314151</v>
+        <v>-4.539579447327525</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8580175632171896</v>
+        <v>0.9033933724118399</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.6677539317908692</v>
+        <v>-0.5455107208985577</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.318929216582076</v>
+        <v>2.392275143117463</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.614635307756</v>
+        <v>-4.501195784769374</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.8707904695828188</v>
+        <v>0.9161662787774691</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.629370269232718</v>
+        <v>-0.5071270583404065</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.339378855459335</v>
+        <v>2.412724781994722</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.437518977720834</v>
+        <v>-4.324079454734208</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.938366030442187</v>
+        <v>0.9837418396368376</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.629370269232718</v>
+        <v>-0.5071270583404065</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.336107884304637</v>
+        <v>2.409453810840025</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.40781685374454</v>
+        <v>-4.294377330757914</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9509302717946175</v>
+        <v>0.9963060809892681</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.6338403944480313</v>
+        <v>-0.5115971835557198</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.334109200937363</v>
+        <v>2.407455127472749</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.228441432505773</v>
+        <v>-4.115001909519147</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.016467415596539</v>
+        <v>1.06184322479119</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.4770636362773126</v>
+        <v>-0.3548204253850011</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.421962231146208</v>
+        <v>2.495308157681595</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.273455646026379</v>
+        <v>-4.160016123039753</v>
       </c>
       <c r="E1958" t="n">
-        <v>0.9792691855198861</v>
+        <v>1.024644994714537</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.5074125315919172</v>
+        <v>-0.3851693206996057</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.384560349289035</v>
+        <v>2.457906275824422</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.540460156298814</v>
+        <v>-4.427020633312188</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.8781589437498578</v>
+        <v>0.9235347529445084</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.7017755696348658</v>
+        <v>-0.5795323587425543</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.273634088802212</v>
+        <v>2.346980015337599</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.530416653950686</v>
+        <v>3.769199504016552</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.627699693788578</v>
+        <v>2.765796265442799</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.540460156298814</v>
+        <v>-4.427020633312188</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8781589437498578</v>
+        <v>0.9235347529445084</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.7017755696348658</v>
+        <v>-0.5795323587425543</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.620763490774946</v>
+        <v>2.758860062429167</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240510.xlsx
+++ b/tame_output/ON/bt/strategyON_20240510.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.8%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>48.8%</t>
+          <t>59.2%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,12 +796,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>49.3%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-21.1%</t>
+          <t>-23.4%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -834,32 +834,32 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.8%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>49.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-35.0%</t>
+          <t>-5.2%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.4%</t>
+          <t>-78.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>113.9%</t>
+          <t>113.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>133.8%</t>
+          <t>133.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-55.7%</t>
+          <t>-55.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.8%</t>
+          <t>-74.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>94.6%</t>
+          <t>94.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.1%</t>
+          <t>-9.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-604.3%</t>
+          <t>-581.0%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-40.9%</t>
+          <t>-42.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-283.9%</t>
+          <t>-276.9%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-32.4%</t>
+          <t>-29.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.5%</t>
+          <t>69.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.47</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>69.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-34.2%</t>
+          <t>-34.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-26.6%</t>
+          <t>-23.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-153.9%</t>
+          <t>-147.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-281.9%</t>
+          <t>-258.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>42.7%</t>
+          <t>49.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.4%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-31.1%</t>
+          <t>-31.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.9%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-170.1%</t>
+          <t>-140.3%</t>
         </is>
       </c>
     </row>
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.44235447177735</v>
+        <v>-9.468790384536863</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.6616929480866514</v>
+        <v>-0.6722673131904568</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.94091562395201</v>
+        <v>-1.967351536711524</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.95105589056683</v>
+        <v>1.935194342911122</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.801884794281351</v>
+        <v>-9.828320707040865</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.8001547737902017</v>
+        <v>-0.8107291388940072</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.94091562395201</v>
+        <v>-1.967351536711524</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.956406193864881</v>
+        <v>1.940544646209172</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.12828482294636</v>
+        <v>-10.15472073570588</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.9227987652990293</v>
+        <v>-0.9333731304028352</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.267315652617023</v>
+        <v>-2.293751565376537</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.76848219662305</v>
+        <v>1.752620648967342</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.34743379102056</v>
+        <v>-10.37386970378008</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.00741660190694</v>
+        <v>-1.017990967010745</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.48646462069122</v>
+        <v>-2.512900533450734</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.640034566400301</v>
+        <v>1.624173018744592</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.34374286606415</v>
+        <v>-10.37017877882366</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.005940231924375</v>
+        <v>-1.016514597028181</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.48646462069122</v>
+        <v>-2.512900533450734</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.640034566400301</v>
+        <v>1.624173018744592</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.54800104139401</v>
+        <v>-10.57443695415353</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.082130304937678</v>
+        <v>-1.092704670041484</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.614103565305209</v>
+        <v>-2.640539478064723</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.56896439675055</v>
+        <v>1.553102849094841</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.76603881302519</v>
+        <v>-10.79247472578471</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.164862859105714</v>
+        <v>-1.175437224209519</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.788874333401108</v>
+        <v>-2.815310246160622</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.468584490377446</v>
+        <v>1.452722942721738</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-10.69256898135774</v>
+        <v>-10.71900489411726</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.120103224945312</v>
+        <v>-1.130677590049118</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.715404501733659</v>
+        <v>-2.741840414493173</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.528038090871337</v>
+        <v>1.512176543215628</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.86769339874429</v>
+        <v>-10.8941293115038</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.175597771152413</v>
+        <v>-1.186172136256219</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.890528919120203</v>
+        <v>-2.916964831879717</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.437518661186927</v>
+        <v>1.421657113531219</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.10214549275878</v>
+        <v>-11.12858140551829</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.276597773659805</v>
+        <v>-1.287172138763611</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.890528919120203</v>
+        <v>-2.916964831879717</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.430299496285331</v>
+        <v>1.414437948629623</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.38994933729601</v>
+        <v>-11.41638525005553</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.398391502248677</v>
+        <v>-1.408965867352482</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.178332763657441</v>
+        <v>-3.204768676416955</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.250944998789012</v>
+        <v>1.235083451133304</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-11.61977378445984</v>
+        <v>-11.64620969721935</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.48920549127565</v>
+        <v>-1.499779856379456</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.340980300727602</v>
+        <v>-3.367416213487116</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.154472266385472</v>
+        <v>1.138610718729764</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-11.8518027041961</v>
+        <v>-11.87823861695562</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.579323330541041</v>
+        <v>-1.589897695644846</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.402992997916025</v>
+        <v>-3.429428910675539</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.119958376701533</v>
+        <v>1.104096829045825</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-11.79978719022729</v>
+        <v>-11.8262231029868</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.554526789267114</v>
+        <v>-1.56510115437092</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.402992997916025</v>
+        <v>-3.429428910675539</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.123948712387933</v>
+        <v>1.108087164732225</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.94145903195141</v>
+        <v>-11.96789494471092</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.612670752855504</v>
+        <v>-1.62324511795931</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.402992997916025</v>
+        <v>-3.429428910675539</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.122473485489192</v>
+        <v>1.106611937833484</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.89186818752657</v>
+        <v>-11.91830410028609</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.577781004920698</v>
+        <v>-1.588355370024504</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.353402153491191</v>
+        <v>-3.379838066250705</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.167281402308964</v>
+        <v>1.151419854653256</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-11.69271608028948</v>
+        <v>-11.71915199304899</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.511171295672541</v>
+        <v>-1.521745660776347</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.188079627541378</v>
+        <v>-3.214515540300892</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.25342378423217</v>
+        <v>1.237562236576461</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.46687092757006</v>
+        <v>-11.49330684032958</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.411254161548568</v>
+        <v>-1.421828526652373</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.146152951954214</v>
+        <v>-3.172588864713728</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.288158862620676</v>
+        <v>1.272297314964968</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.34229227123247</v>
+        <v>-11.36872818399199</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.360283554457472</v>
+        <v>-1.370857919561278</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.146152951954214</v>
+        <v>-3.172588864713728</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.289298007176735</v>
+        <v>1.273436459521027</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.39518755927676</v>
+        <v>-11.42162347203627</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.37880789551308</v>
+        <v>-1.389382260616885</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.141197605865768</v>
+        <v>-3.167633518625282</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.294904988991911</v>
+        <v>1.279043441336202</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.11127882834801</v>
+        <v>-11.13771474110752</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.259510698902943</v>
+        <v>-1.270085064006749</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.141197605865768</v>
+        <v>-3.167633518625282</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.300638693230547</v>
+        <v>1.284777145574839</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.03991243573836</v>
+        <v>-11.06634834849788</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.24070140425295</v>
+        <v>-1.251275769356755</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.069831213256121</v>
+        <v>-3.096267126015634</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.33372126640247</v>
+        <v>1.317859718746762</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.77607556853429</v>
+        <v>-10.80251148129381</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.145050138684229</v>
+        <v>-1.155624503788034</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.069831213256121</v>
+        <v>-3.096267126015634</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.323837785089563</v>
+        <v>1.307976237433855</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.50883376766589</v>
+        <v>-10.53526968042541</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.039987978836244</v>
+        <v>-1.05056234394005</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.069831213256121</v>
+        <v>-3.096267126015634</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.322003224590189</v>
+        <v>1.306141676934481</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.4109267289894</v>
+        <v>-10.43736264174892</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.001125478339108</v>
+        <v>-1.011699843442914</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.001845463395564</v>
+        <v>-3.028281376155078</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.362494359533062</v>
+        <v>1.346632811877354</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.38697318801345</v>
+        <v>-10.41340910077296</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.9908755558032314</v>
+        <v>-1.001449920907037</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.977891922419607</v>
+        <v>-3.00432783517912</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.37753499026413</v>
+        <v>1.361673442608422</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.12291324969065</v>
+        <v>-10.14934916245016</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.8985118966358652</v>
+        <v>-0.9090862617396702</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.713831984096811</v>
+        <v>-2.740267896856324</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.522710637096056</v>
+        <v>1.506849089440348</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.415833626185812</v>
+        <v>-9.442269538945325</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.6184670808942312</v>
+        <v>-0.6290414459980367</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.713831984096811</v>
+        <v>-2.740267896856324</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.519923603435755</v>
+        <v>1.504062055780047</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.375649327819621</v>
+        <v>-9.402085240579135</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.6020497376599137</v>
+        <v>-0.6126241027637191</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.67364768573062</v>
+        <v>-2.700083598490133</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.544377806343311</v>
+        <v>1.528516258687603</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.295579532281817</v>
+        <v>-9.32201544504133</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.5706549982240348</v>
+        <v>-0.5812293633278403</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.593577890192816</v>
+        <v>-2.620013802952329</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.59178650488675</v>
+        <v>1.575924957231042</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.062098310052217</v>
+        <v>-9.088534222811731</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.4693380804943428</v>
+        <v>-0.4799124455981483</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.360096667963217</v>
+        <v>-2.386532580722731</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.739799667062362</v>
+        <v>1.723938119406654</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.882389779908344</v>
+        <v>-8.908825692667858</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.4003468787497524</v>
+        <v>-0.4109212438535579</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.302925163800521</v>
+        <v>-2.329361076560035</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.77121035924702</v>
+        <v>1.755348811591312</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.750114306277457</v>
+        <v>-8.77655021903697</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.3520692025503704</v>
+        <v>-0.3626435676541759</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.170649690169635</v>
+        <v>-2.197085602929148</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.845943130172579</v>
+        <v>1.830081582516871</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.559514631604303</v>
+        <v>-8.585950544363817</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.2730142719934725</v>
+        <v>-0.283588637097278</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.980050015496482</v>
+        <v>-2.006485928255995</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.963117995664107</v>
+        <v>1.947256448008399</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.310514832920722</v>
+        <v>-8.336950745680236</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.1605080112963813</v>
+        <v>-0.1710823764001868</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.980050015496482</v>
+        <v>-2.006485928255995</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.976024336887766</v>
+        <v>1.960162789232058</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.416104822693827</v>
+        <v>-8.44254073545334</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.3307199368048419</v>
+        <v>-0.341294301908647</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.085640005269586</v>
+        <v>-2.1120759180291</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.784694413424685</v>
+        <v>1.768832865768977</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.434839724812424</v>
+        <v>-8.461275637571937</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.2896695557751943</v>
+        <v>-0.3002439208789998</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.085640005269586</v>
+        <v>-2.1120759180291</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.833238755301771</v>
+        <v>1.817377207646063</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.286899683404824</v>
+        <v>-8.313335596164338</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.3503724619003221</v>
+        <v>-0.3609468270041276</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.065319089361029</v>
+        <v>-2.091755002120542</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.725552382158738</v>
+        <v>1.70969083450303</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.262671047015852</v>
+        <v>-8.289106959775365</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.349394993598211</v>
+        <v>-0.3599693587020165</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.041090452972057</v>
+        <v>-2.06752636573157</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.731375577738643</v>
+        <v>1.715514030082935</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.21912264024516</v>
+        <v>-8.245558553004674</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.338936242985028</v>
+        <v>-0.3495106080888331</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.041090452972057</v>
+        <v>-2.06752636573157</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.72441496564355</v>
+        <v>1.708553417987842</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.976974246791302</v>
+        <v>-8.003410159550816</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.2276145312223417</v>
+        <v>-0.2381888963261467</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.041090452972057</v>
+        <v>-2.06752636573157</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.738877320024693</v>
+        <v>1.723015772368985</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.913744875022954</v>
+        <v>-7.940180787782467</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.2077906620558072</v>
+        <v>-0.2183650271596127</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.041090452972057</v>
+        <v>-2.06752636573157</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.733409440483888</v>
+        <v>1.71754789282818</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.790453740205823</v>
+        <v>-7.816889652965337</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.1609761141183781</v>
+        <v>-0.1715504792221831</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.917799318154926</v>
+        <v>-1.94423523091444</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.804882215384743</v>
+        <v>1.789020667729035</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.76930454130238</v>
+        <v>-7.795740454061893</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.1448154563196753</v>
+        <v>-0.1553898214234808</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.896650119251483</v>
+        <v>-1.923086032010997</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.825272712964134</v>
+        <v>1.809411165308426</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.525539099318935</v>
+        <v>-7.551975012078449</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.05152857117924681</v>
+        <v>-0.0621029362830523</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.896650119251483</v>
+        <v>-1.923086032010997</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.821053421311185</v>
+        <v>1.805191873655477</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.261511032125675</v>
+        <v>-7.287946944885189</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.05620696961807337</v>
+        <v>0.04563260451426787</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.69478472043553</v>
+        <v>-1.721220633195043</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.944296974520773</v>
+        <v>1.928435426865065</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.0116606381766</v>
+        <v>-7.038096550936114</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.148889202181405</v>
+        <v>0.1383148370776</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.69478472043553</v>
+        <v>-1.721220633195043</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.937039049504476</v>
+        <v>1.921177501848767</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.835768545709168</v>
+        <v>-6.862204458468682</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.2228451626890267</v>
+        <v>0.2122707975852212</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.69478472043553</v>
+        <v>-1.721220633195043</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.940638173025124</v>
+        <v>1.924776625369416</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.664322082686705</v>
+        <v>-6.690757995446218</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.3047512539525656</v>
+        <v>0.2941768888487606</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.523338257413066</v>
+        <v>-1.54977417017258</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.056833556893156</v>
+        <v>2.040972009237448</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.439289083017882</v>
+        <v>-6.465724995777395</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.3937849314363921</v>
+        <v>0.3832105663325867</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.298305257744243</v>
+        <v>-1.324741170503757</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.190873834310747</v>
+        <v>2.175012286655038</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.224654705381475</v>
+        <v>-6.251090618140989</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.4843334835452722</v>
+        <v>0.4737591184414667</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.083670880107837</v>
+        <v>-1.11010679286735</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.324349261946908</v>
+        <v>2.3084877142912</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.131654664175577</v>
+        <v>-6.15809057693509</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5027277588114267</v>
+        <v>0.4921533937076217</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.083670880107837</v>
+        <v>-1.11010679286735</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.305543520730704</v>
+        <v>2.289681973074996</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.891224167370717</v>
+        <v>-5.91766008013023</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6006430341582485</v>
+        <v>0.590068669054443</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.8432403833029762</v>
+        <v>-0.8696762960624898</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.451544895438497</v>
+        <v>2.435683347782789</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.818981599199522</v>
+        <v>-5.845417511959035</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6334693752615466</v>
+        <v>0.6228950101577411</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.8432403833029762</v>
+        <v>-0.8696762960624898</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.455474209273317</v>
+        <v>2.439612661617609</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.703041749574337</v>
+        <v>-5.72947766233385</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6805238990289606</v>
+        <v>0.6699495339251551</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.7664186522868524</v>
+        <v>-0.7928545650463659</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.502245831800332</v>
+        <v>2.486384284144624</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.460386161151174</v>
+        <v>-5.486822073910687</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7745842056182193</v>
+        <v>0.7640098405144138</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.7664186522868524</v>
+        <v>-0.7928545650463659</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.499243903020325</v>
+        <v>2.483382355364617</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.240365363114163</v>
+        <v>-5.266801275873677</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8641715618436376</v>
+        <v>0.8535971967398321</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.6251988072188721</v>
+        <v>-0.6516347199783856</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.585554847071727</v>
+        <v>2.569693299416019</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.041116733209354</v>
+        <v>-5.067552645968868</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9597651966073846</v>
+        <v>0.9491908315035791</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.6251988072188721</v>
+        <v>-0.6516347199783856</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.60144902987355</v>
+        <v>2.585587482217842</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.881601629689984</v>
+        <v>-4.908037542449498</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.024717082455434</v>
+        <v>1.014142717351629</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.4656837036995022</v>
+        <v>-0.4921196164590157</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.698303936425474</v>
+        <v>2.682442388769766</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.736929484590247</v>
+        <v>-4.76336539734976</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.092674043056769</v>
+        <v>1.082099677952964</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.3210115585997648</v>
+        <v>-0.3474474713592783</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.795195326046757</v>
+        <v>2.779333778391049</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.796804311947939</v>
+        <v>-4.823240224707453</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.054761603515118</v>
+        <v>1.044187238411313</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.3808863859574569</v>
+        <v>-0.4073222987169704</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.745307921033567</v>
+        <v>2.729446373377859</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.710004814168931</v>
+        <v>-4.736440726928445</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.111881895949288</v>
+        <v>1.101307530845482</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.3808863859574569</v>
+        <v>-0.4073222987169704</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.767708414356133</v>
+        <v>2.751846866700425</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.712474520630737</v>
+        <v>-4.738910433390251</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.110966414737977</v>
+        <v>1.100392049634172</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.3833560924192631</v>
+        <v>-0.4097920051787766</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.766298991852462</v>
+        <v>2.750437444196754</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.780844706954747</v>
+        <v>-4.807280619714261</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.094625262683075</v>
+        <v>1.08405089757927</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.3740803933830481</v>
+        <v>-0.4005163061425616</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.782871333748893</v>
+        <v>2.767009786093185</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.659428277328271</v>
+        <v>-4.685864190087784</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.133628543165557</v>
+        <v>1.123054178061752</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.3740803933830481</v>
+        <v>-0.4005163061425616</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.773308042380784</v>
+        <v>2.757446494725076</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.690421436656976</v>
+        <v>-4.71685734941649</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9459408444744617</v>
+        <v>0.9353664793706564</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.3740803933830481</v>
+        <v>-0.4005163061425616</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.598017607421171</v>
+        <v>2.582156059765463</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.514947176864506</v>
+        <v>-4.54138308962402</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.020697780383237</v>
+        <v>1.010123415279432</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.3740803933830481</v>
+        <v>-0.4005163061425616</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.602584839412958</v>
+        <v>2.58672329175725</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.625883429505755</v>
+        <v>-4.652319342265269</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9520653080879449</v>
+        <v>0.9414909429841396</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.3740803933830481</v>
+        <v>-0.4005163061425616</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.578326868174166</v>
+        <v>2.562465320518458</v>
       </c>
     </row>
     <row r="1941">
@@ -46191,19 +46191,19 @@
         <v>3.773206721581293</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.8059064894239</v>
+        <v>2.782896034438447</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.828910007048989</v>
+        <v>-4.596023608010351</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8739860622905571</v>
+        <v>0.9441301669205591</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.5771069709262815</v>
+        <v>-0.3442205718876442</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.459642306868131</v>
+        <v>2.576363691305861</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734162</v>
+        <v>3.784340376734161</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.816078875856032</v>
+        <v>2.793068420870579</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.670984408113696</v>
+        <v>-4.438098009075058</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9473286882968068</v>
+        <v>1.017472792926809</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.5771069709262815</v>
+        <v>-0.3442205718876442</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.469814693300264</v>
+        <v>2.586536077737993</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212299</v>
+        <v>3.786946382212298</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.811025146429893</v>
+        <v>2.788014691444439</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.819305661924824</v>
+        <v>-4.586419262886187</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.8829464573462156</v>
+        <v>0.9530905619762176</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.5771069709262815</v>
+        <v>-0.3442205718876442</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.464760963874124</v>
+        <v>2.581482348311853</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786046</v>
+        <v>3.752023923786045</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.802800921874418</v>
+        <v>2.779790466888965</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.820488746575885</v>
+        <v>-4.587602347537247</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.8742489989303168</v>
+        <v>0.9443931035603188</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.582750019392793</v>
+        <v>-0.3498636203541557</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.453150910238743</v>
+        <v>2.569872294676472</v>
       </c>
     </row>
     <row r="1945">
@@ -46283,19 +46283,19 @@
         <v>3.753567590273191</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.80335279490752</v>
+        <v>2.780342339922067</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.697361039581802</v>
+        <v>-4.464474640543164</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9240519547610517</v>
+        <v>0.9941960593910535</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.582750019392793</v>
+        <v>-0.3498636203541557</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.453702783271844</v>
+        <v>2.570424167709573</v>
       </c>
     </row>
     <row r="1946">
@@ -46306,19 +46306,19 @@
         <v>3.7333870252795</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.732625486798885</v>
+        <v>2.709615031813432</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.604550558130942</v>
+        <v>-4.371664159092305</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.8904488392327612</v>
+        <v>0.9605929438627632</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.4899395379419337</v>
+        <v>-0.2570531389032964</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.438661764033725</v>
+        <v>2.555383148471455</v>
       </c>
     </row>
     <row r="1947">
@@ -46329,19 +46329,19 @@
         <v>3.748282241030427</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.734498962723486</v>
+        <v>2.711488507738033</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.555987505909912</v>
+        <v>-4.323101106871275</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9117475360457741</v>
+        <v>0.9818916406757758</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.4413764857209035</v>
+        <v>-0.2084900866822662</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.469673071290944</v>
+        <v>2.586394455728674</v>
       </c>
     </row>
     <row r="1948">
@@ -46352,19 +46352,19 @@
         <v>3.721073619942739</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.729574671235209</v>
+        <v>2.706564216249756</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.443316287673662</v>
+        <v>-4.210429888635025</v>
       </c>
       <c r="E1948" t="n">
-        <v>0.951891731851997</v>
+        <v>1.022035836481999</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.3287052674846533</v>
+        <v>-0.095818868446016</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.532351510744418</v>
+        <v>2.649072895182147</v>
       </c>
     </row>
     <row r="1949">
@@ -46375,19 +46375,19 @@
         <v>3.743044028268537</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.735065967065876</v>
+        <v>2.712055512080423</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.330939286490989</v>
+        <v>-4.098052887452352</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.002333828155733</v>
+        <v>1.072477932785735</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.3287052674846533</v>
+        <v>-0.095818868446016</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.537842806575084</v>
+        <v>2.654564191012814</v>
       </c>
     </row>
     <row r="1950">
@@ -46398,19 +46398,19 @@
         <v>3.689594264968863</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.746563168834415</v>
+        <v>2.723552713848962</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.52917385537772</v>
+        <v>-4.296287456339082</v>
       </c>
       <c r="E1950" t="n">
-        <v>0.9345372023695802</v>
+        <v>1.004681306999582</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.5269398363713839</v>
+        <v>-0.2940534373327466</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.430399267011585</v>
+        <v>2.547120651449315</v>
       </c>
     </row>
     <row r="1951">
@@ -46421,19 +46421,19 @@
         <v>3.643066046175323</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.584918888835069</v>
+        <v>2.561908433849616</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.612175136402999</v>
+        <v>-4.379288737364361</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.7396924099601219</v>
+        <v>0.8098365145901238</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.5455107208985577</v>
+        <v>-0.3126243218599203</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.257612456295934</v>
+        <v>2.374333840733664</v>
       </c>
     </row>
     <row r="1952">
@@ -46444,19 +46444,19 @@
         <v>3.68271273519927</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.705068549554274</v>
+        <v>2.682058094568821</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.452980864346422</v>
+        <v>-4.220094465307785</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9235197795019583</v>
+        <v>0.9936638841319601</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.5455107208985577</v>
+        <v>-0.3126243218599203</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.37776211701514</v>
+        <v>2.494483501452869</v>
       </c>
     </row>
     <row r="1953">
@@ -46467,19 +46467,19 @@
         <v>3.73300886566077</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.719581575656597</v>
+        <v>2.696571120671144</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.539579447327525</v>
+        <v>-4.306693048288888</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9033933724118399</v>
+        <v>0.9735374770418419</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.5455107208985577</v>
+        <v>-0.3126243218599203</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.392275143117463</v>
+        <v>2.508996527555192</v>
       </c>
     </row>
     <row r="1954">
@@ -46490,19 +46490,19 @@
         <v>3.741170494383425</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.717001016998966</v>
+        <v>2.693990562013513</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.501195784769374</v>
+        <v>-4.268309385730737</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9161662787774691</v>
+        <v>0.9863103834074711</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.5071270583404065</v>
+        <v>-0.2742406593017692</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.412724781994722</v>
+        <v>2.529446166432452</v>
       </c>
     </row>
     <row r="1955">
@@ -46513,19 +46513,19 @@
         <v>3.751143622002486</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.713730045844268</v>
+        <v>2.690719590858815</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.324079454734208</v>
+        <v>-4.09119305569557</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9837418396368376</v>
+        <v>1.053885944266839</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.5071270583404065</v>
+        <v>-0.2742406593017692</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.409453810840025</v>
+        <v>2.526175195277754</v>
       </c>
     </row>
     <row r="1956">
@@ -46536,19 +46536,19 @@
         <v>3.741324873263904</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.714413437606181</v>
+        <v>2.691402982620728</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.294377330757914</v>
+        <v>-4.061490931719277</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9963060809892681</v>
+        <v>1.06645018561927</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.5115971835557198</v>
+        <v>-0.2787107845170825</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.407455127472749</v>
+        <v>2.524176511910479</v>
       </c>
     </row>
     <row r="1957">
@@ -46559,19 +46559,19 @@
         <v>3.750725801481238</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.708200412912595</v>
+        <v>2.685189957927142</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.115001909519147</v>
+        <v>-3.882115510480509</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.06184322479119</v>
+        <v>1.131987329421191</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.3548204253850011</v>
+        <v>-0.1219340263463639</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.495308157681595</v>
+        <v>2.612029542119324</v>
       </c>
     </row>
     <row r="1958">
@@ -46582,19 +46582,19 @@
         <v>3.716988143452233</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.689007868244185</v>
+        <v>2.665997413258732</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.160016123039753</v>
+        <v>-3.927129724001115</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.024644994714537</v>
+        <v>1.094789099344539</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.3851693206996057</v>
+        <v>-0.1522829216609685</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.457906275824422</v>
+        <v>2.574627660262151</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.73702303297954</v>
+        <v>3.737023032979539</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.694699430583131</v>
+        <v>2.671688975597678</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.427020633312188</v>
+        <v>-4.194134234273551</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9235347529445084</v>
+        <v>0.9936788575745101</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.5795323587425543</v>
+        <v>-0.346645959703917</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.346980015337599</v>
+        <v>2.463701399775328</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.769199504016552</v>
+        <v>3.87269310566039</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.765796265442799</v>
+        <v>3.064122709735507</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.427020633312188</v>
+        <v>-4.194134234273551</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9235347529445084</v>
+        <v>0.9936788575745101</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.5795323587425543</v>
+        <v>-0.346645959703917</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.758860062429167</v>
+        <v>3.057186506721875</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240510.xlsx
+++ b/tame_output/ON/bt/strategyON_20240510.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>55.5%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,12 +796,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>33.1%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>49.3%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-23.4%</t>
+          <t>-21.1%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -834,32 +834,32 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>49.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-11.4%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.4%</t>
+          <t>-78.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>113.7%</t>
+          <t>114.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>133.4%</t>
+          <t>133.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>92.4%</t>
+          <t>93.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-55.8%</t>
+          <t>-54.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.6%</t>
+          <t>-75.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>94.4%</t>
+          <t>94.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>444.3%</t>
+          <t>444.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.5%</t>
+          <t>-9.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-581.0%</t>
+          <t>-588.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.7%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,32 +1150,32 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-40.5%</t>
+          <t>-43.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-1.1%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-42.1%</t>
+          <t>-35.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>1.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-276.9%</t>
+          <t>-246.9%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-29.2%</t>
+          <t>-30.7%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.1%</t>
+          <t>70.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-0.44</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>69.7%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>69.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-34.4%</t>
+          <t>-35.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-23.1%</t>
+          <t>-24.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-147.5%</t>
+          <t>-292.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-258.7%</t>
+          <t>-266.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>49.3%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-16.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-140.3%</t>
+          <t>-171.3%</t>
         </is>
       </c>
     </row>
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.32201544504133</v>
+        <v>-9.181311319814386</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.5812293633278403</v>
+        <v>-0.5249477132370624</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.620013802952329</v>
+        <v>-2.479309677725384</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.575924957231042</v>
+        <v>1.660347432367209</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.088534222811731</v>
+        <v>-8.947830097584788</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.4799124455981483</v>
+        <v>-0.4236307955073708</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.386532580722731</v>
+        <v>-2.245828455495785</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.723938119406654</v>
+        <v>1.808360594542821</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.908825692667858</v>
+        <v>-8.768121567440915</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.4109212438535579</v>
+        <v>-0.3546395937627809</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.329361076560035</v>
+        <v>-2.188656951333089</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.755348811591312</v>
+        <v>1.839771286727479</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.77655021903697</v>
+        <v>-8.635846093810027</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.3626435676541759</v>
+        <v>-0.3063619175633989</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.197085602929148</v>
+        <v>-2.056381477702203</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.830081582516871</v>
+        <v>1.914504057653038</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.585950544363817</v>
+        <v>-8.445246419136874</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.283588637097278</v>
+        <v>-0.2273069870065005</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.006485928255995</v>
+        <v>-1.86578180302905</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.947256448008399</v>
+        <v>2.031678923144566</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.336950745680236</v>
+        <v>-8.196246620453293</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.1710823764001868</v>
+        <v>-0.1148007263094093</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.006485928255995</v>
+        <v>-1.86578180302905</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.960162789232058</v>
+        <v>2.044585264368226</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.44254073545334</v>
+        <v>-8.301836610226397</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.341294301908647</v>
+        <v>-0.2850126518178699</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.1120759180291</v>
+        <v>-1.971371792802154</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.768832865768977</v>
+        <v>1.853255340905144</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.461275637571937</v>
+        <v>-8.320571512344994</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.3002439208789998</v>
+        <v>-0.2439622707882223</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.1120759180291</v>
+        <v>-1.971371792802154</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.817377207646063</v>
+        <v>1.901799682782231</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.313335596164338</v>
+        <v>-8.172631470937395</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.3609468270041276</v>
+        <v>-0.3046651769133502</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.091755002120542</v>
+        <v>-1.951050876893597</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.70969083450303</v>
+        <v>1.794113309639197</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.289106959775365</v>
+        <v>-8.148402834548422</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.3599693587020165</v>
+        <v>-0.3036877086112395</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.06752636573157</v>
+        <v>-1.926822240504624</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.715514030082935</v>
+        <v>1.799936505219103</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.245558553004674</v>
+        <v>-8.104854427777731</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.3495106080888331</v>
+        <v>-0.293228957998056</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.06752636573157</v>
+        <v>-1.926822240504624</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.708553417987842</v>
+        <v>1.792975893124009</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-8.003410159550816</v>
+        <v>-7.862706034323873</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.2381888963261467</v>
+        <v>-0.1819072462353697</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.06752636573157</v>
+        <v>-1.926822240504624</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.723015772368985</v>
+        <v>1.807438247505152</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.940180787782467</v>
+        <v>-7.799476662555525</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.2183650271596127</v>
+        <v>-0.1620833770688352</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.06752636573157</v>
+        <v>-1.926822240504624</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.71754789282818</v>
+        <v>1.801970367964348</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.816889652965337</v>
+        <v>-7.676185527738394</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.1715504792221831</v>
+        <v>-0.1152688291314061</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.94423523091444</v>
+        <v>-1.803531105687494</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.789020667729035</v>
+        <v>1.873443142865203</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.795740454061893</v>
+        <v>-7.65503632883495</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.1553898214234808</v>
+        <v>-0.09910817133270378</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.923086032010997</v>
+        <v>-1.782381906784051</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.809411165308426</v>
+        <v>1.893833640444594</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.551975012078449</v>
+        <v>-7.411270886851506</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.0621029362830523</v>
+        <v>-0.005821286192275288</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.923086032010997</v>
+        <v>-1.782381906784051</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.805191873655477</v>
+        <v>1.889614348791645</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.287946944885189</v>
+        <v>-7.147242819658246</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.04563260451426787</v>
+        <v>0.1019142546050449</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.721220633195043</v>
+        <v>-1.580516507968097</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.928435426865065</v>
+        <v>2.012857902001233</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.038096550936114</v>
+        <v>-6.897392425709171</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.1383148370776</v>
+        <v>0.194596487168377</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.721220633195043</v>
+        <v>-1.580516507968097</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.921177501848767</v>
+        <v>2.005599976984935</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.862204458468682</v>
+        <v>-6.721500333241739</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.2122707975852212</v>
+        <v>0.2685524476759986</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.721220633195043</v>
+        <v>-1.580516507968097</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.924776625369416</v>
+        <v>2.009199100505584</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.690757995446218</v>
+        <v>-6.550053870219275</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.2941768888487606</v>
+        <v>0.3504585389395376</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.54977417017258</v>
+        <v>-1.409070044945634</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.040972009237448</v>
+        <v>2.125394484373615</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.465724995777395</v>
+        <v>-6.325020870550452</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.3832105663325867</v>
+        <v>0.4394922164233637</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.324741170503757</v>
+        <v>-1.184037045276811</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.175012286655038</v>
+        <v>2.259434761791206</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.251090618140989</v>
+        <v>-6.110386492914046</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.4737591184414667</v>
+        <v>0.5300407685322437</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.11010679286735</v>
+        <v>-0.9694026676404039</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.3084877142912</v>
+        <v>2.392910189427367</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.15809057693509</v>
+        <v>-6.017386451708147</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.4921533937076217</v>
+        <v>0.5484350437983987</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.11010679286735</v>
+        <v>-0.9694026676404039</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.289681973074996</v>
+        <v>2.374104448211163</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.91766008013023</v>
+        <v>-5.776955954903287</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.590068669054443</v>
+        <v>0.6463503191452205</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.8696762960624898</v>
+        <v>-0.7289721708355437</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.435683347782789</v>
+        <v>2.520105822918957</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.845417511959035</v>
+        <v>-5.704713386732092</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6228950101577411</v>
+        <v>0.6791766602485185</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.8696762960624898</v>
+        <v>-0.7289721708355437</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.439612661617609</v>
+        <v>2.524035136753777</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.72947766233385</v>
+        <v>-5.588773537106907</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.6699495339251551</v>
+        <v>0.7262311840159326</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.7928545650463659</v>
+        <v>-0.6521504398194198</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.486384284144624</v>
+        <v>2.570806759280791</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.486822073910687</v>
+        <v>-5.346117948683744</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.7640098405144138</v>
+        <v>0.8202914906051912</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.7928545650463659</v>
+        <v>-0.6521504398194198</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.483382355364617</v>
+        <v>2.567804830500784</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.266801275873677</v>
+        <v>-5.126097150646734</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.8535971967398321</v>
+        <v>0.9098788468306096</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.6516347199783856</v>
+        <v>-0.5109305947514395</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.569693299416019</v>
+        <v>2.654115774552187</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-5.067552645968868</v>
+        <v>-4.926848520741925</v>
       </c>
       <c r="E1930" t="n">
-        <v>0.9491908315035791</v>
+        <v>1.005472481594356</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.6516347199783856</v>
+        <v>-0.5109305947514395</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.585587482217842</v>
+        <v>2.67000995735401</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.908037542449498</v>
+        <v>-4.767333417222555</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.014142717351629</v>
+        <v>1.070424367442406</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.4921196164590157</v>
+        <v>-0.3514154912320696</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.682442388769766</v>
+        <v>2.766864863905934</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.76336539734976</v>
+        <v>-4.622661272122818</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.082099677952964</v>
+        <v>1.138381328043741</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.3474474713592783</v>
+        <v>-0.2067433461323322</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.779333778391049</v>
+        <v>2.863756253527216</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.823240224707453</v>
+        <v>-4.68253609948051</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.044187238411313</v>
+        <v>1.10046888850209</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.4073222987169704</v>
+        <v>-0.2666181734900243</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.729446373377859</v>
+        <v>2.813868848514027</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.736440726928445</v>
+        <v>-4.595736601701502</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.101307530845482</v>
+        <v>1.157589180936259</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.4073222987169704</v>
+        <v>-0.2666181734900243</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.751846866700425</v>
+        <v>2.836269341836593</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.738910433390251</v>
+        <v>-4.598206308163308</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.100392049634172</v>
+        <v>1.156673699724949</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.4097920051787766</v>
+        <v>-0.2690878799518305</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.750437444196754</v>
+        <v>2.834859919332921</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.807280619714261</v>
+        <v>-4.666576494487318</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.08405089757927</v>
+        <v>1.140332547670047</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.4005163061425616</v>
+        <v>-0.2598121809156155</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.767009786093185</v>
+        <v>2.851432261229352</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.685864190087784</v>
+        <v>-4.545160064860841</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.123054178061752</v>
+        <v>1.179335828152529</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.4005163061425616</v>
+        <v>-0.2598121809156155</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.757446494725076</v>
+        <v>2.841868969861244</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.71685734941649</v>
+        <v>-4.576153224189547</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9353664793706564</v>
+        <v>0.9916481294614337</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.4005163061425616</v>
+        <v>-0.2598121809156155</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.582156059765463</v>
+        <v>2.66657853490163</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.54138308962402</v>
+        <v>-4.400678964397077</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.010123415279432</v>
+        <v>1.066405065370209</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.4005163061425616</v>
+        <v>-0.2598121809156155</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.58672329175725</v>
+        <v>2.671145766893418</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.652319342265269</v>
+        <v>-4.511615217038326</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9414909429841396</v>
+        <v>0.9977725930749166</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.4005163061425616</v>
+        <v>-0.2598121809156155</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.562465320518458</v>
+        <v>2.646887795654625</v>
       </c>
     </row>
     <row r="1941">
@@ -46191,19 +46191,19 @@
         <v>3.773206721581293</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.782896034438447</v>
+        <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.596023608010351</v>
+        <v>-4.490404474039863</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9441301669205591</v>
+        <v>1.009388275494207</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.3442205718876442</v>
+        <v>-0.238601437917153</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.576363691305861</v>
+        <v>2.662745626673608</v>
       </c>
     </row>
     <row r="1942">
@@ -46214,19 +46214,19 @@
         <v>3.784340376734161</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.793068420870579</v>
+        <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.438098009075058</v>
+        <v>-4.33247887510457</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.017472792926809</v>
+        <v>1.082730901500457</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.3442205718876442</v>
+        <v>-0.238601437917153</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.586536077737993</v>
+        <v>2.672918013105741</v>
       </c>
     </row>
     <row r="1943">
@@ -46237,19 +46237,19 @@
         <v>3.786946382212298</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.788014691444439</v>
+        <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.586419262886187</v>
+        <v>-4.480800128915699</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9530905619762176</v>
+        <v>1.018348670549866</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.3442205718876442</v>
+        <v>-0.238601437917153</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.581482348311853</v>
+        <v>2.667864283679601</v>
       </c>
     </row>
     <row r="1944">
@@ -46260,19 +46260,19 @@
         <v>3.752023923786045</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.779790466888965</v>
+        <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.587602347537247</v>
+        <v>-4.48198321356676</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9443931035603188</v>
+        <v>1.009651212133967</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.3498636203541557</v>
+        <v>-0.2442444863836646</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.569872294676472</v>
+        <v>2.65625423004422</v>
       </c>
     </row>
     <row r="1945">
@@ -46283,19 +46283,19 @@
         <v>3.753567590273191</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.780342339922067</v>
+        <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.464474640543164</v>
+        <v>-4.358855506572677</v>
       </c>
       <c r="E1945" t="n">
-        <v>0.9941960593910535</v>
+        <v>1.059454167964701</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.3498636203541557</v>
+        <v>-0.2442444863836646</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.570424167709573</v>
+        <v>2.656806103077321</v>
       </c>
     </row>
     <row r="1946">
@@ -46306,19 +46306,19 @@
         <v>3.7333870252795</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.709615031813432</v>
+        <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.371664159092305</v>
+        <v>-4.266045025121818</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9605929438627632</v>
+        <v>1.025851052436411</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.2570531389032964</v>
+        <v>-0.1514340049328052</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.555383148471455</v>
+        <v>2.641765083839203</v>
       </c>
     </row>
     <row r="1947">
@@ -46329,19 +46329,19 @@
         <v>3.748282241030427</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.711488507738033</v>
+        <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.323101106871275</v>
+        <v>-4.217481972900788</v>
       </c>
       <c r="E1947" t="n">
-        <v>0.9818916406757758</v>
+        <v>1.047149749249424</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.2084900866822662</v>
+        <v>-0.102870952711775</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.586394455728674</v>
+        <v>2.672776391096421</v>
       </c>
     </row>
     <row r="1948">
@@ -46352,19 +46352,19 @@
         <v>3.721073619942739</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.706564216249756</v>
+        <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.210429888635025</v>
+        <v>-4.104810754664538</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.022035836481999</v>
+        <v>1.087293945055647</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.095818868446016</v>
+        <v>0.00980026552447516</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.649072895182147</v>
+        <v>2.735454830549894</v>
       </c>
     </row>
     <row r="1949">
@@ -46375,19 +46375,19 @@
         <v>3.743044028268537</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.712055512080423</v>
+        <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.098052887452352</v>
+        <v>-3.992433753481865</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.072477932785735</v>
+        <v>1.137736041359383</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.095818868446016</v>
+        <v>0.00980026552447516</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.654564191012814</v>
+        <v>2.740946126380562</v>
       </c>
     </row>
     <row r="1950">
@@ -46398,19 +46398,19 @@
         <v>3.689594264968863</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.723552713848962</v>
+        <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.296287456339082</v>
+        <v>-4.190668322368595</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.004681306999582</v>
+        <v>1.06993941557323</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.2940534373327466</v>
+        <v>-0.1884343033622554</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.547120651449315</v>
+        <v>2.633502586817063</v>
       </c>
     </row>
     <row r="1951">
@@ -46421,19 +46421,19 @@
         <v>3.643066046175323</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.561908433849616</v>
+        <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.379288737364361</v>
+        <v>-4.273669603393874</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8098365145901238</v>
+        <v>0.8750946231637717</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.3126243218599203</v>
+        <v>-0.2070051878894292</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.374333840733664</v>
+        <v>2.460715776101412</v>
       </c>
     </row>
     <row r="1952">
@@ -46444,19 +46444,19 @@
         <v>3.68271273519927</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.682058094568821</v>
+        <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.220094465307785</v>
+        <v>-4.114475331337298</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9936638841319601</v>
+        <v>1.058921992705608</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.3126243218599203</v>
+        <v>-0.2070051878894292</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.494483501452869</v>
+        <v>2.580865436820617</v>
       </c>
     </row>
     <row r="1953">
@@ -46467,19 +46467,19 @@
         <v>3.73300886566077</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.696571120671144</v>
+        <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.306693048288888</v>
+        <v>-4.201073914318401</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9735374770418419</v>
+        <v>1.03879558561549</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.3126243218599203</v>
+        <v>-0.2070051878894292</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.508996527555192</v>
+        <v>2.59537846292294</v>
       </c>
     </row>
     <row r="1954">
@@ -46490,19 +46490,19 @@
         <v>3.741170494383425</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.693990562013513</v>
+        <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.268309385730737</v>
+        <v>-4.16269025176025</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9863103834074711</v>
+        <v>1.051568491981119</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.2742406593017692</v>
+        <v>-0.168621525331278</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.529446166432452</v>
+        <v>2.615828101800199</v>
       </c>
     </row>
     <row r="1955">
@@ -46513,19 +46513,19 @@
         <v>3.751143622002486</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.690719590858815</v>
+        <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.09119305569557</v>
+        <v>-3.985573921725083</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.053885944266839</v>
+        <v>1.119144052840487</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.2742406593017692</v>
+        <v>-0.168621525331278</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.526175195277754</v>
+        <v>2.612557130645501</v>
       </c>
     </row>
     <row r="1956">
@@ -46536,19 +46536,19 @@
         <v>3.741324873263904</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.691402982620728</v>
+        <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.061490931719277</v>
+        <v>-3.95587179774879</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.06645018561927</v>
+        <v>1.131708294192918</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.2787107845170825</v>
+        <v>-0.1730916505465914</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.524176511910479</v>
+        <v>2.610558447278227</v>
       </c>
     </row>
     <row r="1957">
@@ -46559,19 +46559,19 @@
         <v>3.750725801481238</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.685189957927142</v>
+        <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.882115510480509</v>
+        <v>-3.776496376510022</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.131987329421191</v>
+        <v>1.197245437994839</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.1219340263463639</v>
+        <v>-0.01631489237587269</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.612029542119324</v>
+        <v>2.698411477487072</v>
       </c>
     </row>
     <row r="1958">
@@ -46582,19 +46582,19 @@
         <v>3.716988143452233</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.665997413258732</v>
+        <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.927129724001115</v>
+        <v>-3.821510590030628</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.094789099344539</v>
+        <v>1.160047207918186</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.1522829216609685</v>
+        <v>-0.0466637876904773</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.574627660262151</v>
+        <v>2.661009595629899</v>
       </c>
     </row>
     <row r="1959">
@@ -46605,19 +46605,19 @@
         <v>3.737023032979539</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.671688975597678</v>
+        <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.194134234273551</v>
+        <v>-4.088515100303064</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9936788575745101</v>
+        <v>1.058936966148158</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.346645959703917</v>
+        <v>-0.2410268257334259</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.463701399775328</v>
+        <v>2.550083335143076</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.87269310566039</v>
+        <v>3.836041154873819</v>
       </c>
       <c r="C1960" t="n">
-        <v>3.064122709735507</v>
+        <v>3.00188907610784</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.194134234273551</v>
+        <v>-4.271709831491195</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9936788575745101</v>
+        <v>1.292848719197615</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.346645959703917</v>
+        <v>-0.4242215569215566</v>
       </c>
       <c r="G1960" t="n">
-        <v>3.057186506721875</v>
+        <v>2.747356141954906</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240510.xlsx
+++ b/tame_output/ON/bt/strategyON_20240510.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>27.9%</t>
         </is>
       </c>
     </row>
@@ -758,12 +758,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>62.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.2%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,32 +849,32 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>49.3%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-5.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-11.4%</t>
+          <t>-23.1%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.9%</t>
+          <t>-79.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>114.3%</t>
+          <t>114.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>133.8%</t>
+          <t>133.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>93.1%</t>
+          <t>92.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-54.0%</t>
+          <t>-55.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.0%</t>
+          <t>-75.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>94.8%</t>
+          <t>94.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>444.6%</t>
+          <t>441.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.1%</t>
+          <t>-9.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-588.7%</t>
+          <t>-595.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1160,17 +1160,17 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-35.6%</t>
+          <t>-38.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>1.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-246.9%</t>
+          <t>-261.3%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-30.7%</t>
+          <t>-31.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.1%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>70.5%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>69.4%</t>
+          <t>68.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.1%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-35.5%</t>
+          <t>-34.2%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-24.3%</t>
+          <t>-25.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>58.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-292.3%</t>
+          <t>-152.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-266.4%</t>
+          <t>-270.1%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-171.3%</t>
+          <t>-185.1%</t>
         </is>
       </c>
     </row>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50044609677668</v>
+        <v>3.500446096776678</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199888</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910631</v>
+        <v>3.49996816391063</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078597</v>
+        <v>3.490055666078596</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587501888027</v>
+        <v>3.485875018880269</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234396</v>
+        <v>3.480688917234395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860585</v>
+        <v>3.493712438860584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767399</v>
+        <v>3.492098065767398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792542</v>
+        <v>3.573670449792541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003468962892</v>
+        <v>3.600034689628919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410717</v>
+        <v>3.691568158410716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240577</v>
+        <v>3.676837974240576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68515780608528</v>
+        <v>3.685157806085279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282101</v>
+        <v>3.6848402482821</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116216</v>
+        <v>3.710931958116215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081568</v>
+        <v>3.768948099081567</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425327</v>
+        <v>3.728574354425326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702411</v>
+        <v>3.74769908470241</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906227</v>
+        <v>3.766313503906226</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781949</v>
+        <v>3.784680945781947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567244</v>
+        <v>3.800825778567242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487773</v>
+        <v>3.789307536487772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309727</v>
+        <v>3.833249172309725</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.83937087185873</v>
+        <v>3.839370871858728</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096476</v>
+        <v>3.856158176096474</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.181311319814386</v>
+        <v>-9.212570383034354</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.5249477132370624</v>
+        <v>-0.5374513385250497</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.479309677725384</v>
+        <v>-2.510568740945353</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.660347432367209</v>
+        <v>1.641591994435228</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761809</v>
+        <v>3.787326853761807</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.947830097584788</v>
+        <v>-8.979089160804754</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.4236307955073708</v>
+        <v>-0.4361344207953577</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.245828455495785</v>
+        <v>-2.277087518715755</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.808360594542821</v>
+        <v>1.789605156610839</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255786</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.768121567440915</v>
+        <v>-8.799380630660881</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.3546395937627809</v>
+        <v>-0.3671432190507673</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.188656951333089</v>
+        <v>-2.219916014553058</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.839771286727479</v>
+        <v>1.821015848795498</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860427</v>
+        <v>3.763178672860425</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.635846093810027</v>
+        <v>-8.667105157029994</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.3063619175633989</v>
+        <v>-0.3188655428513854</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.056381477702203</v>
+        <v>-2.087640540922172</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.914504057653038</v>
+        <v>1.895748619721057</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575953</v>
+        <v>3.784715218575951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.445246419136874</v>
+        <v>-8.47650548235684</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.2273069870065005</v>
+        <v>-0.2398106122944874</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.86578180302905</v>
+        <v>-1.897040866249019</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.031678923144566</v>
+        <v>2.012923485212585</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430987</v>
+        <v>3.753878996430985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.196246620453293</v>
+        <v>-8.227505683673259</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.1148007263094093</v>
+        <v>-0.1273043515973962</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.86578180302905</v>
+        <v>-1.897040866249019</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.044585264368226</v>
+        <v>2.025829826436244</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077643</v>
+        <v>3.692928280077641</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.301836610226397</v>
+        <v>-8.333095673446364</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.2850126518178699</v>
+        <v>-0.2975162771058564</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.971371792802154</v>
+        <v>-2.002630856022123</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.853255340905144</v>
+        <v>1.834499902973163</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.7704190084579</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.320571512344994</v>
+        <v>-8.351830575564961</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.2439622707882223</v>
+        <v>-0.2564658960762092</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.971371792802154</v>
+        <v>-2.002630856022123</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.901799682782231</v>
+        <v>1.883044244850249</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180809</v>
+        <v>3.760330111180807</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.172631470937395</v>
+        <v>-8.203890534157361</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.3046651769133502</v>
+        <v>-0.317168802201337</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.951050876893597</v>
+        <v>-1.982309940113566</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.794113309639197</v>
+        <v>1.775357871707216</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.723562653879201</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.148402834548422</v>
+        <v>-8.179661897768389</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.3036877086112395</v>
+        <v>-0.3161913338992259</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.926822240504624</v>
+        <v>-1.958081303724593</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.799936505219103</v>
+        <v>1.781181067287121</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568106</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.104854427777731</v>
+        <v>-8.136113490997698</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.293228957998056</v>
+        <v>-0.3057325832860425</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.926822240504624</v>
+        <v>-1.958081303724593</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.792975893124009</v>
+        <v>1.774220455192028</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963418</v>
+        <v>3.782918957963417</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.862706034323873</v>
+        <v>-7.893965097543839</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.1819072462353697</v>
+        <v>-0.1944108715233561</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.926822240504624</v>
+        <v>-1.958081303724593</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.807438247505152</v>
+        <v>1.788682809573171</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192817</v>
+        <v>3.828547911192815</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.799476662555525</v>
+        <v>-7.830735725775491</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.1620833770688352</v>
+        <v>-0.1745870023568221</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.926822240504624</v>
+        <v>-1.958081303724593</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.801970367964348</v>
+        <v>1.783214930032366</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262047</v>
+        <v>3.828049353262045</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.676185527738394</v>
+        <v>-7.70744459095836</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.1152688291314061</v>
+        <v>-0.1277724544193926</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.803531105687494</v>
+        <v>-1.834790168907463</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.873443142865203</v>
+        <v>1.854687704933221</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389909</v>
+        <v>3.812450103389907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.65503632883495</v>
+        <v>-7.686295392054917</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.09910817133270378</v>
+        <v>-0.1116117966206902</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.782381906784051</v>
+        <v>-1.81364097000402</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.893833640444594</v>
+        <v>1.875078202512612</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788094</v>
+        <v>3.748324832788092</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.411270886851506</v>
+        <v>-7.442529950071473</v>
       </c>
       <c r="E1917" t="n">
-        <v>-0.005821286192275288</v>
+        <v>-0.01832491148026172</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.782381906784051</v>
+        <v>-1.81364097000402</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.889614348791645</v>
+        <v>1.870858910859663</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527525</v>
+        <v>3.824307657527523</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.147242819658246</v>
+        <v>-7.178501882878212</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.1019142546050449</v>
+        <v>0.08941062931705845</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.580516507968097</v>
+        <v>-1.611775571188066</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.012857902001233</v>
+        <v>1.994102464069251</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749184</v>
+        <v>3.826351398749182</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.897392425709171</v>
+        <v>-6.928651488929138</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.194596487168377</v>
+        <v>0.1820928618803905</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.580516507968097</v>
+        <v>-1.611775571188066</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.005599976984935</v>
+        <v>1.986844539052953</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481497</v>
+        <v>3.835954411481495</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.721500333241739</v>
+        <v>-6.752759396461705</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.2685524476759986</v>
+        <v>0.2560488223880117</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.580516507968097</v>
+        <v>-1.611775571188066</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.009199100505584</v>
+        <v>1.990443662573602</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862987</v>
+        <v>3.780930335862985</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.550053870219275</v>
+        <v>-6.581312933439242</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.3504585389395376</v>
+        <v>0.3379549136515512</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.409070044945634</v>
+        <v>-1.440329108165603</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.125394484373615</v>
+        <v>2.106639046441634</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102782</v>
+        <v>3.77376164710278</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.325020870550452</v>
+        <v>-6.356279933770419</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.4394922164233637</v>
+        <v>0.4269885911353772</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.184037045276811</v>
+        <v>-1.21529610849678</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.259434761791206</v>
+        <v>2.240679323859224</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353074</v>
+        <v>3.764614304353072</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.110386492914046</v>
+        <v>-6.141645556134012</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5300407685322437</v>
+        <v>0.5175371432442573</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.9694026676404039</v>
+        <v>-1.000661730860373</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.392910189427367</v>
+        <v>2.374154751495386</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544783</v>
+        <v>3.798811195544781</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-6.017386451708147</v>
+        <v>-6.048645514928114</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.5484350437983987</v>
+        <v>0.5359314185104123</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.9694026676404039</v>
+        <v>-1.000661730860373</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.374104448211163</v>
+        <v>2.355349010279181</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712294</v>
+        <v>3.797691308712293</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.776955954903287</v>
+        <v>-5.808215018123254</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.6463503191452205</v>
+        <v>0.6338466938572336</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.7289721708355437</v>
+        <v>-0.7602312340555129</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.520105822918957</v>
+        <v>2.501350384986975</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837686</v>
+        <v>3.821589933837684</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.704713386732092</v>
+        <v>-5.735972449952059</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.6791766602485185</v>
+        <v>0.6666730349605317</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.7289721708355437</v>
+        <v>-0.7602312340555129</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.524035136753777</v>
+        <v>2.505279698821795</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349967</v>
+        <v>3.822323422349966</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.588773537106907</v>
+        <v>-5.620032600326874</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.7262311840159326</v>
+        <v>0.7137275587279457</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.6521504398194198</v>
+        <v>-0.683409503039389</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.570806759280791</v>
+        <v>2.552051321348809</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972341</v>
+        <v>3.84861305097234</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.346117948683744</v>
+        <v>-5.377377011903711</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.8202914906051912</v>
+        <v>0.8077878653172044</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.6521504398194198</v>
+        <v>-0.683409503039389</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.567804830500784</v>
+        <v>2.549049392568803</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145941</v>
+        <v>3.818665376145939</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-5.126097150646734</v>
+        <v>-5.1573562138667</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9098788468306096</v>
+        <v>0.8973752215426227</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.5109305947514395</v>
+        <v>-0.5421896579714087</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.654115774552187</v>
+        <v>2.635360336620205</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009953</v>
+        <v>3.843270952009951</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.926848520741925</v>
+        <v>-4.990981749801125</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.005472481594356</v>
+        <v>0.9798191899706763</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.5109305947514395</v>
+        <v>-0.5421896579714087</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.67000995735401</v>
+        <v>2.651254519422029</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504381096626</v>
+        <v>3.845043810966258</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.767333417222555</v>
+        <v>-4.831466646281755</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.070424367442406</v>
+        <v>1.044771075818726</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.3514154912320696</v>
+        <v>-0.3826745544520388</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.766864863905934</v>
+        <v>2.748109425973952</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046997</v>
+        <v>3.791269976046995</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.622661272122818</v>
+        <v>-4.686794501182018</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.138381328043741</v>
+        <v>1.112728036420061</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.2067433461323322</v>
+        <v>-0.2380024093523014</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.863756253527216</v>
+        <v>2.845000815595235</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412104</v>
+        <v>3.735835647412102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.68253609948051</v>
+        <v>-4.74666932853971</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.10046888850209</v>
+        <v>1.07481559687841</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.2666181734900243</v>
+        <v>-0.2978772367099935</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.813868848514027</v>
+        <v>2.795113410582045</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144517</v>
+        <v>3.762643902144515</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.595736601701502</v>
+        <v>-4.659869830760702</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.157589180936259</v>
+        <v>1.131935889312579</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.2666181734900243</v>
+        <v>-0.2978772367099935</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.836269341836593</v>
+        <v>2.817513903904612</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900695</v>
+        <v>3.729142822900693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.598206308163308</v>
+        <v>-4.662339537222508</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.156673699724949</v>
+        <v>1.131020408101269</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.2690878799518305</v>
+        <v>-0.3003469431717997</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.834859919332921</v>
+        <v>2.81610448140094</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473602</v>
+        <v>3.7432166204736</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.666576494487318</v>
+        <v>-4.730709723546518</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.140332547670047</v>
+        <v>1.114679256046367</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.2598121809156155</v>
+        <v>-0.2910712441355847</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.851432261229352</v>
+        <v>2.832676823297371</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978371</v>
+        <v>3.714175563978369</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.545160064860841</v>
+        <v>-4.609293293920041</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.179335828152529</v>
+        <v>1.153682536528849</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.2598121809156155</v>
+        <v>-0.2910712441355847</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.841868969861244</v>
+        <v>2.823113531929262</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887705</v>
+        <v>3.710903155887703</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.576153224189547</v>
+        <v>-4.640286453248747</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9916481294614337</v>
+        <v>0.9659948378377536</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.2598121809156155</v>
+        <v>-0.2910712441355847</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.66657853490163</v>
+        <v>2.647823096969649</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675903</v>
+        <v>3.746038950675901</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.400678964397077</v>
+        <v>-4.464812193456277</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.066405065370209</v>
+        <v>1.040751773746529</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.2598121809156155</v>
+        <v>-0.2910712441355847</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.671145766893418</v>
+        <v>2.652390328961437</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695448</v>
+        <v>3.765020747695446</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.511615217038326</v>
+        <v>-4.575748446097526</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9977725930749166</v>
+        <v>0.9721193014512366</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.2598121809156155</v>
+        <v>-0.2910712441355847</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.646887795654625</v>
+        <v>2.628132357722644</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581293</v>
+        <v>3.773206721581291</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.490404474039863</v>
+        <v>-4.778775023640759</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.009388275494207</v>
+        <v>0.894040055653849</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.238601437917153</v>
+        <v>-0.4940978216788181</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.662745626673608</v>
+        <v>2.509447796416609</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734161</v>
+        <v>3.78434037673416</v>
       </c>
       <c r="C1942" t="n">
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.33247887510457</v>
+        <v>-4.620849424705466</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.082730901500457</v>
+        <v>0.9673826816600986</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.238601437917153</v>
+        <v>-0.4940978216788181</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.672918013105741</v>
+        <v>2.519620182848742</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212298</v>
+        <v>3.786946382212296</v>
       </c>
       <c r="C1943" t="n">
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.480800128915699</v>
+        <v>-4.769170678516595</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.018348670549866</v>
+        <v>0.9030004507095073</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.238601437917153</v>
+        <v>-0.4940978216788181</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.667864283679601</v>
+        <v>2.514566453422602</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786045</v>
+        <v>3.752023923786044</v>
       </c>
       <c r="C1944" t="n">
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.48198321356676</v>
+        <v>-4.770353763167655</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.009651212133967</v>
+        <v>0.8943029922936088</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.2442444863836646</v>
+        <v>-0.4997408701453296</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.65625423004422</v>
+        <v>2.50295639978722</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273191</v>
+        <v>3.753567590273189</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.358855506572677</v>
+        <v>-4.647226056173572</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.059454167964701</v>
+        <v>0.9441059481243435</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.2442444863836646</v>
+        <v>-0.4997408701453296</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.656806103077321</v>
+        <v>2.503508272820322</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333870252795</v>
+        <v>3.733387025279498</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.266045025121818</v>
+        <v>-4.554415574722713</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.025851052436411</v>
+        <v>0.9105028325960529</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.1514340049328052</v>
+        <v>-0.4069303886944703</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.641765083839203</v>
+        <v>2.488467253582203</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030427</v>
+        <v>3.748282241030426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.217481972900788</v>
+        <v>-4.505852522501683</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.047149749249424</v>
+        <v>0.9318015294090658</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.102870952711775</v>
+        <v>-0.3583673364734401</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.672776391096421</v>
+        <v>2.519478560839422</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942739</v>
+        <v>3.721073619942738</v>
       </c>
       <c r="C1948" t="n">
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.104810754664538</v>
+        <v>-4.393181304265433</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.087293945055647</v>
+        <v>0.9719457252152888</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.00980026552447516</v>
+        <v>-0.2456961182371899</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.735454830549894</v>
+        <v>2.582157000292896</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268537</v>
+        <v>3.743044028268535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.992433753481865</v>
+        <v>-4.28080430308276</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.137736041359383</v>
+        <v>1.022387821519025</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.00980026552447516</v>
+        <v>-0.2456961182371899</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.740946126380562</v>
+        <v>2.587648296123563</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968863</v>
+        <v>3.689594264968861</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.190668322368595</v>
+        <v>-4.47903887196949</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.06993941557323</v>
+        <v>0.9545911957328719</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1884343033622554</v>
+        <v>-0.4439306871239205</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.633502586817063</v>
+        <v>2.480204756560064</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175323</v>
+        <v>3.643066046175321</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.273669603393874</v>
+        <v>-4.562040152994769</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8750946231637717</v>
+        <v>0.7597464033234136</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.2070051878894292</v>
+        <v>-0.4625015716510942</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.460715776101412</v>
+        <v>2.307417945844413</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.68271273519927</v>
+        <v>3.682712735199268</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.114475331337298</v>
+        <v>-4.402845880938193</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.058921992705608</v>
+        <v>0.94357377286525</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.2070051878894292</v>
+        <v>-0.4625015716510942</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.580865436820617</v>
+        <v>2.427567606563618</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.73300886566077</v>
+        <v>3.733008865660768</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.201073914318401</v>
+        <v>-4.489444463919296</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.03879558561549</v>
+        <v>0.9234473657751319</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.2070051878894292</v>
+        <v>-0.4625015716510942</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.59537846292294</v>
+        <v>2.442080632665941</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383425</v>
+        <v>3.741170494383423</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.16269025176025</v>
+        <v>-4.451060801361145</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.051568491981119</v>
+        <v>0.9362202721407609</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.168621525331278</v>
+        <v>-0.4241179090929431</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.615828101800199</v>
+        <v>2.4625302715432</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002486</v>
+        <v>3.751143622002484</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.985573921725083</v>
+        <v>-4.273944471325978</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.119144052840487</v>
+        <v>1.003795833000129</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.168621525331278</v>
+        <v>-0.4241179090929431</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.612557130645501</v>
+        <v>2.459259300388502</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263904</v>
+        <v>3.741324873263902</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.95587179774879</v>
+        <v>-4.244242347349685</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.131708294192918</v>
+        <v>1.01636007435256</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.1730916505465914</v>
+        <v>-0.4285880343082564</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.610558447278227</v>
+        <v>2.457260617021228</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481238</v>
+        <v>3.750725801481236</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.776496376510022</v>
+        <v>-4.064866926110917</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.197245437994839</v>
+        <v>1.081897218154481</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.01631489237587269</v>
+        <v>-0.2718112761375377</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.698411477487072</v>
+        <v>2.545113647230073</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452233</v>
+        <v>3.716988143452231</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.821510590030628</v>
+        <v>-4.109881139631524</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.160047207918186</v>
+        <v>1.044698988077828</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.0466637876904773</v>
+        <v>-0.3021601714521424</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.661009595629899</v>
+        <v>2.5077117653729</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979539</v>
+        <v>3.737023032979538</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.088515100303064</v>
+        <v>-4.376885649903959</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.058936966148158</v>
+        <v>0.9435887463078001</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.2410268257334259</v>
+        <v>-0.4965232094950909</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.550083335143076</v>
+        <v>2.396785504886076</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.836041154873819</v>
+        <v>3.560264152590144</v>
       </c>
       <c r="C1960" t="n">
-        <v>3.00188907610784</v>
+        <v>2.885706425187318</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.271709831491195</v>
+        <v>-4.341188597391093</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.292848719197615</v>
+        <v>1.148874561917133</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.4242215569215566</v>
+        <v>-0.4608261569822252</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.747356141954906</v>
+        <v>2.609210730997983</v>
       </c>
     </row>
   </sheetData>
